--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -441,7 +441,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>1M Supporting Demand</t>
+          <t>1M Supporting Zone</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
@@ -451,7 +451,7 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>1D Execution Demand</t>
+          <t>1D Execution Zone</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -461,17 +461,17 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Curve Location (Ep 7)</t>
+          <t>Sector Bonus (Ep 16)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
+          <t>GTF Combo Score</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
           <t>Setup Status</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>Action</t>
         </is>
       </c>
     </row>
@@ -482,41 +482,41 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>1418.23</v>
+        <v>3532.18</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1211.8</t>
+          <t>3320.3 - 3461.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>449.6</t>
+          <t>3426.2 - 3496.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
@@ -527,41 +527,41 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>944.52</v>
+        <v>5690.98</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>810.3</t>
+          <t>5349.5 - 5577.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>767.5</t>
+          <t>5520.2 - 5634.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
@@ -572,41 +572,41 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4343.94</v>
+        <v>10114.94</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3963.3</t>
+          <t>9508.0 - 9912.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>2742.1</t>
+          <t>9811.5 - 10013.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
@@ -617,41 +617,41 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4293.18</v>
+        <v>9441.450000000001</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3219.9</t>
+          <t>8875.0 - 9252.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>3925.9</t>
+          <t>9158.2 - 9347.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
@@ -662,41 +662,41 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>12983.97</v>
+        <v>10925.63</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>11614.8</t>
+          <t>10270.1 - 10707.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>3346.1</t>
+          <t>10597.9 - 10816.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
@@ -707,1926 +707,1926 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>1862.42</v>
+        <v>5166.07</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1534.4</t>
+          <t>4856.1 - 5062.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5011.1 - 5114.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4550</v>
+        <v>303.08</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>4115.8</t>
+          <t>284.9 - 297.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>3046.9</t>
+          <t>294.0 - 300.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4344.29</v>
+        <v>7217.45</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>3388.2</t>
+          <t>6784.4 - 7073.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7000.9 - 7145.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>1973.7</v>
+        <v>952.75</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1800.3</t>
+          <t>895.6 - 933.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>924.2 - 943.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>11269.06</v>
+        <v>1723.67</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7570.3</t>
+          <t>1620.2 - 1689.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>4557.5</t>
+          <t>1672.0 - 1706.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>BRITANNIA</t>
+          <t>CIPLA</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2008.03</v>
+        <v>14859.32</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1787.2</t>
+          <t>13967.8 - 14562.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>1325.8</t>
+          <t>14413.5 - 14710.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CIPLA</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1028.17</v>
+        <v>2190.61</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>786.3</t>
+          <t>2059.2 - 2146.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>432.0</t>
+          <t>2124.9 - 2168.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>16686.08</v>
+        <v>533.62</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>13117.6</t>
+          <t>501.6 - 523.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>13568.0</t>
+          <t>517.6 - 528.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>DIVISLAB</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>5042.11</v>
+        <v>21908.02</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4606.6</t>
+          <t>20593.5 - 21469.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>21250.8 - 21688.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4473.52</v>
+        <v>4889.72</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3927.9</t>
+          <t>4596.3 - 4791.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4743.0 - 4840.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>7390</v>
+        <v>1051.48</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6407.7</t>
+          <t>988.4 - 1030.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1019.9 - 1041.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>689.66</v>
+        <v>1565.1</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>482.8</t>
+          <t>1471.2 - 1533.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1518.1 - 1549.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>HCLTECH</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1054.9</v>
+        <v>730.65</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>911.5</t>
+          <t>686.8 - 716.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>708.7 - 723.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>SELL SETUP READY (High Curve)</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>SELL @ ZONE</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>17770.76</v>
+        <v>10047.87</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>15460.5</t>
+          <t>9445.0 - 9846.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9746.4 - 9947.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>26062.45</v>
+        <v>5009.84</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>11374.7</t>
+          <t>4709.3 - 4909.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>10406.2</t>
+          <t>4859.5 - 4959.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>HINDALCO</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>4547.81</v>
+        <v>5375.14</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4576.9</t>
+          <t>5052.6 - 5267.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>3384.0</t>
+          <t>5213.9 - 5321.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>HINDALCO</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2793.51</v>
+        <v>4307.2</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>2506.3</t>
+          <t>4048.8 - 4221.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4178.0 - 4264.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>9439.709999999999</v>
+        <v>3174.65</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>7382.1</t>
+          <t>2984.2 - 3111.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>6044.1</t>
+          <t>3079.4 - 3142.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>635.64</v>
+        <v>4583.23</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>438.1</t>
+          <t>4308.2 - 4491.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>456.7</t>
+          <t>4445.7 - 4537.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1024.04</v>
+        <v>862.92</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1082.1</t>
+          <t>811.1 - 845.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>837.0 - 854.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>3354.44</v>
+        <v>1299.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>3168.6</t>
+          <t>1221.5 - 1273.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1850.9</t>
+          <t>1260.5 - 1286.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>6754.38</v>
+        <v>1782.3</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>5427.4</t>
+          <t>1675.4 - 1746.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3128.0</t>
+          <t>1728.8 - 1764.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>LARSEN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1139.07</v>
+        <v>5812.56</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>918.1</t>
+          <t>5463.8 - 5696.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>8.0/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5638.2 - 5754.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LTIM</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>4322.7</v>
+        <v>1095.3</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>4037.8</t>
+          <t>1029.6 - 1073.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1062.4 - 1084.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1690.03</v>
+        <v>4191.16</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1484.2</t>
+          <t>3939.7 - 4107.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4065.4 - 4149.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>7938.25</v>
+        <v>9175.110000000001</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>6128.6</t>
+          <t>8624.6 - 8991.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>6788.6</t>
+          <t>8899.9 - 9083.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>4211.08</v>
+        <v>7880.52</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>3562.9</t>
+          <t>7407.7 - 7722.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7644.1 - 7801.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>14001.03</v>
+        <v>18071.53</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>13040.1</t>
+          <t>16987.2 - 17710.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>9178.3</t>
+          <t>17529.4 - 17890.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>ONGC</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>3794.62</v>
+        <v>5798.34</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>3514.0</t>
+          <t>5450.4 - 5682.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5624.4 - 5740.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>8768.799999999999</v>
+        <v>7944.74</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7561.0</t>
+          <t>7468.1 - 7785.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7706.4 - 7865.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>6223.06</v>
+        <v>1325</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>4364.5</t>
+          <t>1245.5 - 1298.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>8.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1285.2 - 1311.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2068.23</v>
+        <v>2688.13</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2082.4</t>
+          <t>2526.8 - 2634.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2607.5 - 2661.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>7585.34</v>
+        <v>1085</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>7504.8</t>
+          <t>1019.9 - 1063.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>8.0/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>3597.3</t>
+          <t>1052.5 - 1074.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1641.37</v>
+        <v>1945</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1461.0</t>
+          <t>1828.3 - 1906.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1886.6 - 1925.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>7812.56</v>
+        <v>2125.71</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>7038.1</t>
+          <t>1998.2 - 2083.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2061.9 - 2104.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>7853.54</v>
+        <v>436.8</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7438.9</t>
+          <t>410.6 - 428.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>2721.4</t>
+          <t>423.7 - 432.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>496.57</v>
+        <v>191.6</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>180.1 - 187.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>185.9 - 189.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>8439.190000000001</v>
+        <v>2467.1</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>7627.5</t>
+          <t>2319.1 - 2417.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2393.1 - 2442.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1549.41</v>
+        <v>1604.14</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1479.5</t>
+          <t>1507.9 - 1572.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>888.8</t>
+          <t>1556.0 - 1588.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>5259.94</v>
+        <v>3736.45</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>4593.2</t>
+          <t>3512.3 - 3661.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>4291.8</t>
+          <t>3624.4 - 3699.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>13325.88</v>
+        <v>4265.77</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>9369.5</t>
+          <t>4009.8 - 4180.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>3636.0</t>
+          <t>4137.8 - 4223.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>BUY READY</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>10230.93</v>
+        <v>2021.3</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>8597.2</t>
+          <t>1960.7 - 2081.9 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>7.5/10 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>4517.9</t>
+          <t>2001.1 - 2061.7 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>HIGH ON CURVE - SELL</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>7358.29</v>
+        <v>1820.4</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>6390.2</t>
+          <t>1765.8 - 1875.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>9.0/10 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>1802.2 - 1856.8 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
@@ -2638,40 +2638,40 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>995.53</v>
+        <v>1490.6</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>976.8</t>
+          <t>1445.9 - 1535.3 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>518.4</t>
+          <t>1475.7 - 1520.4 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>6.0/10 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>LOW ON CURVE - BUY</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
@@ -2683,40 +2683,40 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>2513.01</v>
+        <v>371.71</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>2171.8</t>
+          <t>360.6 - 382.9 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>9.5/10 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>368.0 - 379.1 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM - TREND</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>WAIT FOR DAILY PULLBACK</t>
+          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>3532.18</v>
+        <v>2614.19</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3320.3 - 3461.5 DBR DEMAND</t>
+          <t>2457.3 - 2561.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3426.2 - 3496.9 DBR DEMAND</t>
+          <t>2535.8 - 2588.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5690.98</v>
+        <v>5036.98</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>5349.5 - 5577.2 DBR DEMAND</t>
+          <t>4734.8 - 4936.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>5520.2 - 5634.1 DBR DEMAND</t>
+          <t>4885.9 - 4986.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10114.94</v>
+        <v>5310.07</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>9508.0 - 9912.6 DBR DEMAND</t>
+          <t>4991.5 - 5203.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>9811.5 - 10013.8 DBR DEMAND</t>
+          <t>5150.8 - 5257.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>9441.450000000001</v>
+        <v>4579.9</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>8875.0 - 9252.6 DBR DEMAND</t>
+          <t>4305.1 - 4488.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9158.2 - 9347.0 DBR DEMAND</t>
+          <t>4442.5 - 4534.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>10925.63</v>
+        <v>1245.6</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>10270.1 - 10707.1 DBR DEMAND</t>
+          <t>1170.9 - 1220.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>10597.9 - 10816.4 DBR DEMAND</t>
+          <t>1208.2 - 1233.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>5166.07</v>
+        <v>3334.62</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>4856.1 - 5062.8 DBR DEMAND</t>
+          <t>3134.5 - 3267.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>5011.1 - 5114.4 DBR DEMAND</t>
+          <t>3234.6 - 3301.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>303.08</v>
+        <v>6940.5</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>284.9 - 297.0 DBR DEMAND</t>
+          <t>6524.1 - 6801.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>294.0 - 300.0 DBR DEMAND</t>
+          <t>6732.3 - 6871.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>7217.45</v>
+        <v>2624.3</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6784.4 - 7073.1 DBR DEMAND</t>
+          <t>2466.8 - 2571.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>7000.9 - 7145.3 DBR DEMAND</t>
+          <t>2545.6 - 2598.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>952.75</v>
+        <v>13570.97</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>895.6 - 933.7 DBR DEMAND</t>
+          <t>12756.7 - 13299.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>924.2 - 943.2 DBR DEMAND</t>
+          <t>13163.8 - 13435.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>1723.67</v>
+        <v>7648.58</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1620.2 - 1689.2 DBR DEMAND</t>
+          <t>7189.7 - 7495.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>1672.0 - 1706.4 DBR DEMAND</t>
+          <t>7419.1 - 7572.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>14859.32</v>
+        <v>2613.99</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>13967.8 - 14562.1 DBR DEMAND</t>
+          <t>2457.2 - 2561.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>14413.5 - 14710.7 DBR DEMAND</t>
+          <t>2535.6 - 2587.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2190.61</v>
+        <v>2958.33</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2059.2 - 2146.8 DBR DEMAND</t>
+          <t>2780.8 - 2899.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2124.9 - 2168.7 DBR DEMAND</t>
+          <t>2869.6 - 2928.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>533.62</v>
+        <v>13052.85</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>501.6 - 523.0 DBR DEMAND</t>
+          <t>12269.7 - 12791.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>517.6 - 528.3 DBR DEMAND</t>
+          <t>12661.3 - 12922.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>21908.02</v>
+        <v>17736.86</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>20593.5 - 21469.9 DBR DEMAND</t>
+          <t>16672.7 - 17382.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>21250.8 - 21688.9 DBR DEMAND</t>
+          <t>17204.8 - 17559.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>4889.72</v>
+        <v>3352.95</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4596.3 - 4791.9 DBR DEMAND</t>
+          <t>3151.8 - 3285.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>4743.0 - 4840.8 DBR DEMAND</t>
+          <t>3252.4 - 3319.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1051.48</v>
+        <v>6974.6</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>988.4 - 1030.4 DBR DEMAND</t>
+          <t>6556.1 - 6835.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>1019.9 - 1041.0 DBR DEMAND</t>
+          <t>6765.4 - 6904.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1565.1</v>
+        <v>720.45</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1471.2 - 1533.8 DBR DEMAND</t>
+          <t>677.2 - 706.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>1518.1 - 1549.4 DBR DEMAND</t>
+          <t>698.8 - 713.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>10047.87</v>
+        <v>3476.52</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>9445.0 - 9846.9 DBR DEMAND</t>
+          <t>3267.9 - 3407.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9746.4 - 9947.4 DBR DEMAND</t>
+          <t>3372.2 - 3441.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5009.84</v>
+        <v>5549.37</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4709.3 - 4909.6 DBR DEMAND</t>
+          <t>5216.4 - 5438.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>4859.5 - 4959.7 DBR DEMAND</t>
+          <t>5382.9 - 5493.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>5375.14</v>
+        <v>7310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>5052.6 - 5267.6 DBR DEMAND</t>
+          <t>6871.4 - 7163.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>5213.9 - 5321.4 DBR DEMAND</t>
+          <t>7090.7 - 7236.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>4307.2</v>
+        <v>479.53</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4048.8 - 4221.1 DBR DEMAND</t>
+          <t>450.8 - 469.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>4178.0 - 4264.1 DBR DEMAND</t>
+          <t>465.1 - 474.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>3174.65</v>
+        <v>1195.3</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>2984.2 - 3111.2 DBR DEMAND</t>
+          <t>1123.6 - 1171.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>3079.4 - 3142.9 DBR DEMAND</t>
+          <t>1159.4 - 1183.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>4583.23</v>
+        <v>3393.8</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>4308.2 - 4491.6 DBR DEMAND</t>
+          <t>3190.2 - 3325.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>4445.7 - 4537.4 DBR DEMAND</t>
+          <t>3292.0 - 3359.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>862.92</v>
+        <v>12528.74</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>811.1 - 845.7 DBR DEMAND</t>
+          <t>11777.0 - 12278.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>837.0 - 854.3 DBR DEMAND</t>
+          <t>12152.9 - 12403.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1782.3</v>
+        <v>1785.4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1675.4 - 1746.7 DBR DEMAND</t>
+          <t>1678.3 - 1749.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1728.8 - 1764.5 DBR DEMAND</t>
+          <t>1731.8 - 1767.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>5812.56</v>
+        <v>1573.15</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>5463.8 - 5696.3 DBR DEMAND</t>
+          <t>1478.8 - 1541.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>5638.2 - 5754.4 DBR DEMAND</t>
+          <t>1526.0 - 1557.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>1095.3</v>
+        <v>3709.87</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>1029.6 - 1073.4 DBR DEMAND</t>
+          <t>3487.3 - 3635.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>1062.4 - 1084.3 DBR DEMAND</t>
+          <t>3598.6 - 3672.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1787,11 +1787,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>4191.16</v>
+        <v>12431.99</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>3939.7 - 4107.3 DBR DEMAND</t>
+          <t>11686.1 - 12183.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>4065.4 - 4149.2 DBR DEMAND</t>
+          <t>12059.0 - 12307.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1832,11 +1832,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>9175.110000000001</v>
+        <v>17884.76</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>8624.6 - 8991.6 DBR DEMAND</t>
+          <t>16811.7 - 17527.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>8899.9 - 9083.4 DBR DEMAND</t>
+          <t>17348.2 - 17705.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1877,11 +1877,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>7880.52</v>
+        <v>1289.31</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>7407.7 - 7722.9 DBR DEMAND</t>
+          <t>1212.0 - 1263.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>7644.1 - 7801.7 DBR DEMAND</t>
+          <t>1250.6 - 1276.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>18071.53</v>
+        <v>5070.95</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>16987.2 - 17710.1 DBR DEMAND</t>
+          <t>4766.7 - 4969.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>17529.4 - 17890.8 DBR DEMAND</t>
+          <t>4918.8 - 5020.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>5798.34</v>
+        <v>520.83</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>5450.4 - 5682.4 DBR DEMAND</t>
+          <t>489.6 - 510.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>5624.4 - 5740.4 DBR DEMAND</t>
+          <t>505.2 - 515.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2012,11 +2012,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>7944.74</v>
+        <v>14255</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>7468.1 - 7785.8 DBR DEMAND</t>
+          <t>13399.7 - 13969.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>7706.4 - 7865.3 DBR DEMAND</t>
+          <t>13827.4 - 14112.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2688.13</v>
+        <v>3021.11</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2526.8 - 2634.4 DBR DEMAND</t>
+          <t>2839.8 - 2960.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2607.5 - 2661.2 DBR DEMAND</t>
+          <t>2930.5 - 2990.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2143,15 +2143,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1085</v>
+        <v>1945</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1019.9 - 1063.3 DBR DEMAND</t>
+          <t>1828.3 - 1906.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1052.5 - 1074.2 DBR DEMAND</t>
+          <t>1886.6 - 1925.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,15 +2188,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1945</v>
+        <v>4556.86</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>1828.3 - 1906.1 DBR DEMAND</t>
+          <t>4283.4 - 4465.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>1886.6 - 1925.5 DBR DEMAND</t>
+          <t>4420.2 - 4511.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,15 +2233,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2125.71</v>
+        <v>436.8</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>1998.2 - 2083.2 DBR DEMAND</t>
+          <t>410.6 - 428.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>2061.9 - 2104.5 DBR DEMAND</t>
+          <t>423.7 - 432.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2278,15 +2278,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>436.8</v>
+        <v>191.6</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>410.6 - 428.1 DBR DEMAND</t>
+          <t>180.1 - 187.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>423.7 - 432.4 DBR DEMAND</t>
+          <t>185.9 - 189.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2323,15 +2323,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>191.6</v>
+        <v>1490.6</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>180.1 - 187.8 DBR DEMAND</t>
+          <t>1401.2 - 1460.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>185.9 - 189.7 DBR DEMAND</t>
+          <t>1445.9 - 1475.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,15 +2368,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>2467.1</v>
+        <v>6039.88</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>2319.1 - 2417.8 DBR DEMAND</t>
+          <t>5677.5 - 5919.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>2393.1 - 2442.4 DBR DEMAND</t>
+          <t>5858.7 - 5979.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2413,15 +2413,15 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1604.14</v>
+        <v>4624.22</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1507.9 - 1572.1 DBR DEMAND</t>
+          <t>4346.8 - 4531.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>1556.0 - 1588.1 DBR DEMAND</t>
+          <t>4485.5 - 4578.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2441,12 +2441,12 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>11.5 / 10 🚀 SUPER COMBO</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
@@ -2458,15 +2458,15 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>3736.45</v>
+        <v>371.71</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3512.3 - 3661.7 DBR DEMAND</t>
+          <t>349.4 - 364.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -2476,7 +2476,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>3624.4 - 3699.1 DBR DEMAND</t>
+          <t>360.6 - 368.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>10.5 / 10 🔥 HIGH COMBO</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
@@ -2507,11 +2507,11 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>4265.77</v>
+        <v>2226.49</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>4009.8 - 4180.5 DBR DEMAND</t>
+          <t>2092.9 - 2182.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -2521,7 +2521,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>4137.8 - 4223.1 DBR DEMAND</t>
+          <t>2159.7 - 2204.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2548,60 +2548,60 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>2021.3</v>
+        <v>1071</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1960.7 - 2081.9 RBD SUPPLY</t>
+          <t>1040.0 - 1100.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>2001.1 - 2061.7 RBD SUPPLY</t>
+          <t>1040.0 - 1050.0 DR DEMAND (WAIT)</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
+          <t>8.0 / 10 ⏳ WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>INFY</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>1820.4</v>
+        <v>2021.3</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>1765.8 - 1875.0 RBD SUPPLY</t>
+          <t>2001.0 - 2061.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>1802.2 - 1856.8 RBD SUPPLY</t>
+          <t>2001.0 - 2061.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2626,27 +2626,27 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
+          <t>8.5 / 10 🔴 SUPPLY HIT</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>1490.6</v>
+        <v>1820.4</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>1445.9 - 1535.3 RBD SUPPLY</t>
+          <t>1810.0 - 1860.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>1475.7 - 1520.4 RBD SUPPLY</t>
+          <t>1800.0 - 1850.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2676,22 +2676,22 @@
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>371.71</v>
+        <v>2467.1</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>360.6 - 382.9 RBD SUPPLY</t>
+          <t>2450.0 - 2510.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>368.0 - 379.1 RBD SUPPLY</t>
+          <t>2440.0 - 2490.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2721,7 +2721,7 @@
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>MONITOR</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I51"/>
+  <dimension ref="A1:I49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2614.19</v>
+        <v>2995.5</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2457.3 - 2561.9 DBR DEMAND</t>
+          <t>2815.8 - 2935.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2535.8 - 2588.1 DBR DEMAND</t>
+          <t>2905.6 - 2965.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -511,7 +511,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5036.98</v>
+        <v>1668.2</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4734.8 - 4936.2 DBR DEMAND</t>
+          <t>1568.1 - 1634.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>4885.9 - 4986.6 DBR DEMAND</t>
+          <t>1618.2 - 1651.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5310.07</v>
+        <v>8750.5</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>4991.5 - 5203.9 DBR DEMAND</t>
+          <t>8225.5 - 8575.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>5150.8 - 5257.0 DBR DEMAND</t>
+          <t>8488.0 - 8663.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -601,7 +601,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4579.9</v>
+        <v>2735.5</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>4305.1 - 4488.3 DBR DEMAND</t>
+          <t>2571.4 - 2680.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>4442.5 - 4534.1 DBR DEMAND</t>
+          <t>2653.4 - 2708.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -646,7 +646,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1245.6</v>
+        <v>1229.8</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1170.9 - 1220.7 DBR DEMAND</t>
+          <t>1156.0 - 1205.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1208.2 - 1233.1 DBR DEMAND</t>
+          <t>1192.9 - 1217.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -691,7 +691,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3334.62</v>
+        <v>11717</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>3134.5 - 3267.9 DBR DEMAND</t>
+          <t>11014.0 - 11482.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>3234.6 - 3301.3 DBR DEMAND</t>
+          <t>11365.5 - 11599.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>6940.5</v>
+        <v>1093.3</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6524.1 - 6801.7 DBR DEMAND</t>
+          <t>1027.7 - 1071.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>6732.3 - 6871.1 DBR DEMAND</t>
+          <t>1060.5 - 1082.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2624.3</v>
+        <v>1915.2</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>2466.8 - 2571.8 DBR DEMAND</t>
+          <t>1800.3 - 1876.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>2545.6 - 2598.1 DBR DEMAND</t>
+          <t>1857.7 - 1896.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -826,7 +826,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>13570.97</v>
+        <v>317.8</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>12756.7 - 13299.5 DBR DEMAND</t>
+          <t>298.7 - 311.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>13163.8 - 13435.3 DBR DEMAND</t>
+          <t>308.3 - 314.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>7648.58</v>
+        <v>5598</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>7189.7 - 7495.6 DBR DEMAND</t>
+          <t>5262.1 - 5486.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>7419.1 - 7572.1 DBR DEMAND</t>
+          <t>5430.1 - 5542.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
@@ -932,11 +932,11 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2613.99</v>
+        <v>1463</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>2457.2 - 2561.7 DBR DEMAND</t>
+          <t>1375.2 - 1433.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -946,7 +946,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>2535.6 - 2587.9 DBR DEMAND</t>
+          <t>1419.1 - 1448.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -961,7 +961,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2958.33</v>
+        <v>412.6</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2780.8 - 2899.2 DBR DEMAND</t>
+          <t>387.8 - 404.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>2869.6 - 2928.7 DBR DEMAND</t>
+          <t>400.2 - 408.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>13052.85</v>
+        <v>8578.5</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>12269.7 - 12791.8 DBR DEMAND</t>
+          <t>8063.8 - 8406.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>12661.3 - 12922.3 DBR DEMAND</t>
+          <t>8321.1 - 8492.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1051,7 +1051,7 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>17736.86</v>
+        <v>1205</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>16672.7 - 17382.1 DBR DEMAND</t>
+          <t>1132.7 - 1180.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>17204.8 - 17559.5 DBR DEMAND</t>
+          <t>1168.8 - 1193.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1096,7 +1096,7 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>3352.95</v>
+        <v>8000</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3151.8 - 3285.9 DBR DEMAND</t>
+          <t>7520.0 - 7840.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>3252.4 - 3319.4 DBR DEMAND</t>
+          <t>7760.0 - 7920.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1141,7 +1141,7 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>6974.6</v>
+        <v>3322.2</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>6556.1 - 6835.1 DBR DEMAND</t>
+          <t>3122.9 - 3255.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>6765.4 - 6904.9 DBR DEMAND</t>
+          <t>3222.5 - 3289.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
@@ -1202,11 +1202,11 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>720.45</v>
+        <v>1365.4</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>677.2 - 706.0 DBR DEMAND</t>
+          <t>1283.5 - 1338.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>698.8 - 713.2 DBR DEMAND</t>
+          <t>1324.4 - 1351.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
@@ -1247,11 +1247,11 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>730.65</v>
+        <v>729</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>686.8 - 716.0 DBR DEMAND</t>
+          <t>685.3 - 714.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1261,7 +1261,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>708.7 - 723.3 DBR DEMAND</t>
+          <t>707.1 - 721.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1276,7 +1276,7 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>3476.52</v>
+        <v>536</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>3267.9 - 3407.0 DBR DEMAND</t>
+          <t>503.8 - 525.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>3372.2 - 3441.8 DBR DEMAND</t>
+          <t>519.9 - 530.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1321,7 +1321,7 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5549.37</v>
+        <v>5865.5</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5216.4 - 5438.4 DBR DEMAND</t>
+          <t>5513.6 - 5748.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5382.9 - 5493.9 DBR DEMAND</t>
+          <t>5689.5 - 5806.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1366,7 +1366,7 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>7310</v>
+        <v>1049.1</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>6871.4 - 7163.8 DBR DEMAND</t>
+          <t>986.2 - 1028.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7090.7 - 7236.9 DBR DEMAND</t>
+          <t>1017.6 - 1038.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1411,7 +1411,7 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>479.53</v>
+        <v>2064.9</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>450.8 - 469.9 DBR DEMAND</t>
+          <t>1941.0 - 2023.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>465.1 - 474.7 DBR DEMAND</t>
+          <t>2003.0 - 2044.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -1468,15 +1468,15 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1195.3</v>
+        <v>1008.9</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>1123.6 - 1171.4 DBR DEMAND</t>
+          <t>948.4 - 988.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>1159.4 - 1183.3 DBR DEMAND</t>
+          <t>978.6 - 998.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -1513,15 +1513,15 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>3393.8</v>
+        <v>279</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>3190.2 - 3325.9 DBR DEMAND</t>
+          <t>262.3 - 273.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>3292.0 - 3359.9 DBR DEMAND</t>
+          <t>270.6 - 276.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
@@ -1558,15 +1558,15 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>12528.74</v>
+        <v>1283.4</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>11777.0 - 12278.2 DBR DEMAND</t>
+          <t>1206.4 - 1257.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>12152.9 - 12403.5 DBR DEMAND</t>
+          <t>1244.9 - 1270.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1591,7 +1591,7 @@
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
@@ -1603,15 +1603,15 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>1299.5</v>
+        <v>392.9</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>1221.5 - 1273.5 DBR DEMAND</t>
+          <t>369.3 - 385.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>1260.5 - 1286.5 DBR DEMAND</t>
+          <t>381.1 - 389.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1636,7 +1636,7 @@
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
@@ -1648,15 +1648,15 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>1785.4</v>
+        <v>4037.4</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>1678.3 - 1749.7 DBR DEMAND</t>
+          <t>3795.2 - 3956.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>1731.8 - 1767.5 DBR DEMAND</t>
+          <t>3916.3 - 3997.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1681,7 +1681,7 @@
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
@@ -1693,15 +1693,15 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>LARSEN</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1573.15</v>
+        <v>3460.1</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>1478.8 - 1541.7 DBR DEMAND</t>
+          <t>3252.5 - 3390.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>1526.0 - 1557.4 DBR DEMAND</t>
+          <t>3356.3 - 3425.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1726,7 +1726,7 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
@@ -1738,15 +1738,15 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>LTIM</t>
+          <t>MARUTI</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>3709.87</v>
+        <v>13990</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>3487.3 - 3635.7 DBR DEMAND</t>
+          <t>13150.6 - 13710.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>3598.6 - 3672.8 DBR DEMAND</t>
+          <t>13570.3 - 13850.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1766,12 +1766,12 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
@@ -1783,15 +1783,15 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>12431.99</v>
+        <v>1493.2</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>11686.1 - 12183.3 DBR DEMAND</t>
+          <t>1403.6 - 1463.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>12059.0 - 12307.7 DBR DEMAND</t>
+          <t>1448.4 - 1478.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
@@ -1828,15 +1828,15 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>MARUTI</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>17884.76</v>
+        <v>338.45</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>16811.7 - 17527.1 DBR DEMAND</t>
+          <t>318.1 - 331.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>17348.2 - 17705.9 DBR DEMAND</t>
+          <t>328.3 - 335.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
@@ -1873,15 +1873,15 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>1289.31</v>
+        <v>267.95</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>1212.0 - 1263.5 DBR DEMAND</t>
+          <t>251.9 - 262.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>1250.6 - 1276.4 DBR DEMAND</t>
+          <t>259.9 - 265.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -1918,15 +1918,15 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>5070.95</v>
+        <v>1323.9</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>4766.7 - 4969.5 DBR DEMAND</t>
+          <t>1244.5 - 1297.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>4918.8 - 5020.2 DBR DEMAND</t>
+          <t>1284.2 - 1310.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
@@ -1963,15 +1963,15 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ONGC</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>520.83</v>
+        <v>1837.6</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>489.6 - 510.4 DBR DEMAND</t>
+          <t>1727.3 - 1800.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>505.2 - 515.6 DBR DEMAND</t>
+          <t>1782.5 - 1819.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
@@ -2008,15 +2008,15 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>14255</v>
+        <v>1942</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>13399.7 - 13969.9 DBR DEMAND</t>
+          <t>1825.5 - 1903.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>13827.4 - 14112.5 DBR DEMAND</t>
+          <t>1883.7 - 1922.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2036,12 +2036,12 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -2053,15 +2053,15 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1325</v>
+        <v>1078</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1245.5 - 1298.5 DBR DEMAND</t>
+          <t>1013.3 - 1056.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1285.2 - 1311.8 DBR DEMAND</t>
+          <t>1045.7 - 1067.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
@@ -2098,15 +2098,15 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>3021.11</v>
+        <v>188.25</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>2839.8 - 2960.7 DBR DEMAND</t>
+          <t>177.0 - 184.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>2930.5 - 2990.9 DBR DEMAND</t>
+          <t>182.6 - 186.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
@@ -2143,15 +2143,15 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1945</v>
+        <v>1643</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1828.3 - 1906.1 DBR DEMAND</t>
+          <t>1544.4 - 1610.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1886.6 - 1925.5 DBR DEMAND</t>
+          <t>1593.7 - 1626.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
@@ -2188,15 +2188,15 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>4556.86</v>
+        <v>5128</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4283.4 - 4465.7 DBR DEMAND</t>
+          <t>4820.3 - 5025.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4420.2 - 4511.3 DBR DEMAND</t>
+          <t>4974.2 - 5076.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2216,12 +2216,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2233,15 +2233,15 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>436.8</v>
+        <v>347.6</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>410.6 - 428.1 DBR DEMAND</t>
+          <t>326.7 - 340.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>423.7 - 432.4 DBR DEMAND</t>
+          <t>337.2 - 344.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2266,7 +2266,7 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
@@ -2278,15 +2278,15 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>191.6</v>
+        <v>11780</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>180.1 - 187.8 DBR DEMAND</t>
+          <t>11073.2 - 11544.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>185.9 - 189.7 DBR DEMAND</t>
+          <t>11426.6 - 11662.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2311,7 +2311,7 @@
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
@@ -2323,15 +2323,15 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1490.6</v>
+        <v>568</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>1401.2 - 1460.8 DBR DEMAND</t>
+          <t>533.9 - 556.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>1445.9 - 1475.7 DBR DEMAND</t>
+          <t>551.0 - 562.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2356,7 +2356,7 @@
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
@@ -2368,15 +2368,15 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>6039.88</v>
+        <v>184.6</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>5677.5 - 5919.1 DBR DEMAND</t>
+          <t>173.5 - 180.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>5858.7 - 5979.5 DBR DEMAND</t>
+          <t>179.1 - 182.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2401,7 +2401,7 @@
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="I44" t="inlineStr">
@@ -2413,195 +2413,195 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4624.22</v>
+        <v>1066</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>4346.8 - 4531.7 DBR DEMAND</t>
+          <t>1040.0 - 1100.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>4485.5 - 4578.0 DBR DEMAND</t>
+          <t>1040.0 - 1050.0 DR DEMAND (WAIT)</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>11.5 / 10 🚀 SUPER COMBO</t>
+          <t>8.0 / 10 WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="I45" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>371.71</v>
+        <v>2032</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>349.4 - 364.3 DBR DEMAND</t>
+          <t>2001.0 - 2061.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>360.6 - 368.0 DBR DEMAND</t>
+          <t>2001.0 - 2061.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>8.5 / 10 SUPPLY HIT</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>2226.49</v>
+        <v>1429.6</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>2092.9 - 2182.0 DBR DEMAND</t>
+          <t>1430.0 - 1500.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>2159.7 - 2204.2 DBR DEMAND</t>
+          <t>1430.0 - 1460.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>9.5 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>10.5 / 10 🔥 HIGH COMBO</t>
+          <t>8.5 / 10 SUPPLY HIT</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>INFY</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1071</v>
+        <v>1190.7</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>1040.0 - 1100.0 RD SUPPLY</t>
+          <t>1810.0 - 1860.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>1040.0 - 1050.0 DR DEMAND (WAIT)</t>
+          <t>1800.0 - 1850.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>0.0 PTS</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>8.0 / 10 ⏳ WAIT FOR PULLBACK</t>
+          <t>8.5 / 10 SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>SUPPLY TEST</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2021.3</v>
+        <v>2445.7</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>2001.0 - 2061.0 RBD SUPPLY</t>
+          <t>2450.0 - 2510.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -2611,7 +2611,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>2001.0 - 2061.0 RBD SUPPLY</t>
+          <t>2440.0 - 2490.0 RBD SUPPLY</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2626,100 +2626,10 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>8.5 / 10 🔴 SUPPLY HIT</t>
+          <t>8.5 / 10 SUPPLY NEAR</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B50" t="n">
-        <v>1820.4</v>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>1810.0 - 1860.0 RBD SUPPLY</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
-      <c r="E50" t="inlineStr">
-        <is>
-          <t>1800.0 - 1850.0 RBD SUPPLY</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>0.0 PTS</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>SUPPLY TEST</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>TCS</t>
-        </is>
-      </c>
-      <c r="B51" t="n">
-        <v>2467.1</v>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>2450.0 - 2510.0 RBD SUPPLY</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>2440.0 - 2490.0 RBD SUPPLY</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>0.0 PTS</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>8.5 / 10 ⚠️ SUPPLY NEAR</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -482,11 +482,11 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>2995.5</v>
+        <v>2985.7</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>2815.8 - 2935.6 DBR DEMAND</t>
+          <t>2806.6 - 2926.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -496,7 +496,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>2905.6 - 2965.5 DBR DEMAND</t>
+          <t>2896.1 - 2955.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -527,11 +527,11 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>1668.2</v>
+        <v>1665</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1568.1 - 1634.8 DBR DEMAND</t>
+          <t>1565.1 - 1631.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -541,7 +541,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>1618.2 - 1651.5 DBR DEMAND</t>
+          <t>1615.0 - 1648.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -572,11 +572,11 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>8750.5</v>
+        <v>8597</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>8225.5 - 8575.5 DBR DEMAND</t>
+          <t>8081.2 - 8425.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -586,7 +586,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>8488.0 - 8663.0 DBR DEMAND</t>
+          <t>8339.1 - 8511.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -617,11 +617,11 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>2735.5</v>
+        <v>2740</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>2571.4 - 2680.8 DBR DEMAND</t>
+          <t>2575.6 - 2685.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -631,7 +631,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>2653.4 - 2708.1 DBR DEMAND</t>
+          <t>2657.8 - 2712.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -662,11 +662,11 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>1229.8</v>
+        <v>1230</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1156.0 - 1205.2 DBR DEMAND</t>
+          <t>1156.2 - 1205.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -676,7 +676,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>1192.9 - 1217.5 DBR DEMAND</t>
+          <t>1193.1 - 1217.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -707,11 +707,11 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>11717</v>
+        <v>11700</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>11014.0 - 11482.7 DBR DEMAND</t>
+          <t>10998.0 - 11466.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -721,7 +721,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>11365.5 - 11599.8 DBR DEMAND</t>
+          <t>11349.0 - 11583.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -752,11 +752,11 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>1093.3</v>
+        <v>1094.2</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1027.7 - 1071.4 DBR DEMAND</t>
+          <t>1028.5 - 1072.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -766,7 +766,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>1060.5 - 1082.4 DBR DEMAND</t>
+          <t>1061.4 - 1083.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -797,11 +797,11 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>1915.2</v>
+        <v>1945</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1800.3 - 1876.9 DBR DEMAND</t>
+          <t>1828.3 - 1906.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>1857.7 - 1896.0 DBR DEMAND</t>
+          <t>1886.6 - 1925.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -842,11 +842,11 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>317.8</v>
+        <v>317</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>298.7 - 311.4 DBR DEMAND</t>
+          <t>298.0 - 310.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -856,7 +856,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>308.3 - 314.6 DBR DEMAND</t>
+          <t>307.5 - 313.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -887,11 +887,11 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>5598</v>
+        <v>5645.5</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>5262.1 - 5486.0 DBR DEMAND</t>
+          <t>5306.8 - 5532.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>5430.1 - 5542.0 DBR DEMAND</t>
+          <t>5476.1 - 5589.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -977,11 +977,11 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>412.6</v>
+        <v>409.3</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>387.8 - 404.3 DBR DEMAND</t>
+          <t>384.7 - 401.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -991,7 +991,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>400.2 - 408.5 DBR DEMAND</t>
+          <t>397.0 - 405.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1022,11 +1022,11 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>8578.5</v>
+        <v>8600</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>8063.8 - 8406.9 DBR DEMAND</t>
+          <t>8084.0 - 8428.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1036,7 +1036,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>8321.1 - 8492.7 DBR DEMAND</t>
+          <t>8342.0 - 8514.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1067,11 +1067,11 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1205</v>
+        <v>1200</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1132.7 - 1180.9 DBR DEMAND</t>
+          <t>1128.0 - 1176.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>1168.8 - 1193.0 DBR DEMAND</t>
+          <t>1164.0 - 1188.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>8000</v>
+        <v>8049</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>7520.0 - 7840.0 DBR DEMAND</t>
+          <t>7566.1 - 7888.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7760.0 - 7920.0 DBR DEMAND</t>
+          <t>7807.5 - 7968.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1157,11 +1157,11 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>3322.2</v>
+        <v>3307.8</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3122.9 - 3255.8 DBR DEMAND</t>
+          <t>3109.3 - 3241.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>3222.5 - 3289.0 DBR DEMAND</t>
+          <t>3208.6 - 3274.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1292,11 +1292,11 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>503.8 - 525.3 DBR DEMAND</t>
+          <t>504.8 - 526.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>519.9 - 530.6 DBR DEMAND</t>
+          <t>520.9 - 531.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1337,11 +1337,11 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>5865.5</v>
+        <v>5895</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5513.6 - 5748.2 DBR DEMAND</t>
+          <t>5541.3 - 5777.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -1351,7 +1351,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>5689.5 - 5806.8 DBR DEMAND</t>
+          <t>5718.1 - 5836.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1382,11 +1382,11 @@
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1049.1</v>
+        <v>1078.5</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>986.2 - 1028.1 DBR DEMAND</t>
+          <t>1013.8 - 1056.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>1017.6 - 1038.6 DBR DEMAND</t>
+          <t>1046.1 - 1067.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1427,11 +1427,11 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>2064.9</v>
+        <v>2063</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1941.0 - 2023.6 DBR DEMAND</t>
+          <t>1939.2 - 2021.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>2003.0 - 2044.3 DBR DEMAND</t>
+          <t>2001.1 - 2042.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1472,11 +1472,11 @@
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1008.9</v>
+        <v>1017.5</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>948.4 - 988.7 DBR DEMAND</t>
+          <t>956.4 - 997.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>978.6 - 998.8 DBR DEMAND</t>
+          <t>987.0 - 1007.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1517,11 +1517,11 @@
         </is>
       </c>
       <c r="B25" t="n">
-        <v>279</v>
+        <v>276.15</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>262.3 - 273.4 DBR DEMAND</t>
+          <t>259.6 - 270.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>270.6 - 276.2 DBR DEMAND</t>
+          <t>267.9 - 273.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1562,11 +1562,11 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>1283.4</v>
+        <v>1269.1</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>1206.4 - 1257.7 DBR DEMAND</t>
+          <t>1193.0 - 1243.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -1576,7 +1576,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>1244.9 - 1270.6 DBR DEMAND</t>
+          <t>1231.0 - 1256.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1607,11 +1607,11 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>392.9</v>
+        <v>390.5</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>369.3 - 385.0 DBR DEMAND</t>
+          <t>367.1 - 382.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -1621,7 +1621,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>381.1 - 389.0 DBR DEMAND</t>
+          <t>378.8 - 386.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>4037.4</v>
+        <v>4020</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>3795.2 - 3956.7 DBR DEMAND</t>
+          <t>3778.8 - 3939.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1666,7 +1666,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>3916.3 - 3997.0 DBR DEMAND</t>
+          <t>3899.4 - 3979.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1697,11 +1697,11 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>3460.1</v>
+        <v>3403.6</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>3252.5 - 3390.9 DBR DEMAND</t>
+          <t>3199.4 - 3335.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>3356.3 - 3425.5 DBR DEMAND</t>
+          <t>3301.5 - 3369.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1742,11 +1742,11 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>13990</v>
+        <v>13875</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>13150.6 - 13710.2 DBR DEMAND</t>
+          <t>13042.5 - 13597.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>13570.3 - 13850.1 DBR DEMAND</t>
+          <t>13458.8 - 13736.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1787,11 +1787,11 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>1493.2</v>
+        <v>1507</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>1403.6 - 1463.3 DBR DEMAND</t>
+          <t>1416.6 - 1476.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -1801,7 +1801,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>1448.4 - 1478.3 DBR DEMAND</t>
+          <t>1461.8 - 1491.9 DBR DEMAND</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1832,11 +1832,11 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>338.45</v>
+        <v>339.45</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>318.1 - 331.7 DBR DEMAND</t>
+          <t>319.1 - 332.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -1846,7 +1846,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>328.3 - 335.1 DBR DEMAND</t>
+          <t>329.3 - 336.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1877,11 +1877,11 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>267.95</v>
+        <v>269.45</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>251.9 - 262.6 DBR DEMAND</t>
+          <t>253.3 - 264.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -1891,7 +1891,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>259.9 - 265.3 DBR DEMAND</t>
+          <t>261.4 - 266.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1922,11 +1922,11 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>1323.9</v>
+        <v>1329</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>1244.5 - 1297.4 DBR DEMAND</t>
+          <t>1249.3 - 1302.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -1936,7 +1936,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>1284.2 - 1310.7 DBR DEMAND</t>
+          <t>1289.1 - 1315.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1967,11 +1967,11 @@
         </is>
       </c>
       <c r="B35" t="n">
-        <v>1837.6</v>
+        <v>1830</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>1727.3 - 1800.8 DBR DEMAND</t>
+          <t>1720.2 - 1793.4 DBR DEMAND</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -1981,7 +1981,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>1782.5 - 1819.2 DBR DEMAND</t>
+          <t>1775.1 - 1811.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -2012,11 +2012,11 @@
         </is>
       </c>
       <c r="B36" t="n">
-        <v>1942</v>
+        <v>1944</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>1825.5 - 1903.2 DBR DEMAND</t>
+          <t>1827.4 - 1905.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>1883.7 - 1922.6 DBR DEMAND</t>
+          <t>1885.7 - 1924.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -2057,11 +2057,11 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>1078</v>
+        <v>1061.9</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>1013.3 - 1056.4 DBR DEMAND</t>
+          <t>998.2 - 1040.7 DBR DEMAND</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>1045.7 - 1067.2 DBR DEMAND</t>
+          <t>1030.0 - 1051.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -2102,11 +2102,11 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>188.25</v>
+        <v>186.2</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>177.0 - 184.5 DBR DEMAND</t>
+          <t>175.0 - 182.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -2116,7 +2116,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>182.6 - 186.4 DBR DEMAND</t>
+          <t>180.6 - 184.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -2147,11 +2147,11 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1643</v>
+        <v>1625</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>1544.4 - 1610.1 DBR DEMAND</t>
+          <t>1527.5 - 1592.5 DBR DEMAND</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>1593.7 - 1626.6 DBR DEMAND</t>
+          <t>1576.2 - 1608.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -2192,11 +2192,11 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>5128</v>
+        <v>5099</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>4820.3 - 5025.4 DBR DEMAND</t>
+          <t>4793.1 - 4997.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>4974.2 - 5076.7 DBR DEMAND</t>
+          <t>4946.0 - 5048.0 DBR DEMAND</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -2237,11 +2237,11 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>347.6</v>
+        <v>343</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>326.7 - 340.6 DBR DEMAND</t>
+          <t>322.4 - 336.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -2251,7 +2251,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>337.2 - 344.1 DBR DEMAND</t>
+          <t>332.7 - 339.6 DBR DEMAND</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -2282,11 +2282,11 @@
         </is>
       </c>
       <c r="B42" t="n">
-        <v>11780</v>
+        <v>11891</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>11073.2 - 11544.4 DBR DEMAND</t>
+          <t>11177.5 - 11653.2 DBR DEMAND</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2296,7 +2296,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>11426.6 - 11662.2 DBR DEMAND</t>
+          <t>11534.3 - 11772.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -2327,11 +2327,11 @@
         </is>
       </c>
       <c r="B43" t="n">
-        <v>568</v>
+        <v>570.5</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>533.9 - 556.6 DBR DEMAND</t>
+          <t>536.3 - 559.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>551.0 - 562.3 DBR DEMAND</t>
+          <t>553.4 - 564.8 DBR DEMAND</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -2372,11 +2372,11 @@
         </is>
       </c>
       <c r="B44" t="n">
-        <v>184.6</v>
+        <v>183.94</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>173.5 - 180.9 DBR DEMAND</t>
+          <t>172.9 - 180.3 DBR DEMAND</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>179.1 - 182.8 DBR DEMAND</t>
+          <t>178.4 - 182.1 DBR DEMAND</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -2417,7 +2417,7 @@
         </is>
       </c>
       <c r="B45" t="n">
-        <v>1066</v>
+        <v>1082</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -2462,7 +2462,7 @@
         </is>
       </c>
       <c r="B46" t="n">
-        <v>2032</v>
+        <v>2020.5</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -2507,7 +2507,7 @@
         </is>
       </c>
       <c r="B47" t="n">
-        <v>1429.6</v>
+        <v>1431.7</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -2552,7 +2552,7 @@
         </is>
       </c>
       <c r="B48" t="n">
-        <v>1190.7</v>
+        <v>1176.1</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -2597,7 +2597,7 @@
         </is>
       </c>
       <c r="B49" t="n">
-        <v>2445.7</v>
+        <v>2349.7</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P155"/>
+  <dimension ref="A1:P162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -532,7 +532,7 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5681.1</v>
+        <v>5675</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>ANANDRATHI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Adani Green Energy Ltd.</t>
+          <t>Anand Rathi Wealth Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,31 +612,31 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>1293</v>
+        <v>2171.1</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>1291.4 - 1302.1 DR DEMAND</t>
+          <t>2167.9 - 2174.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>765.0 - 814.2 DR DEMAND</t>
+          <t>1710.6 - 1725.35 DR DEMAND</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -673,17 +673,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>HINDUNILVR</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Hindustan Unilever Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>2020.7</v>
+        <v>1180</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2016.0 - 2022.7 DR DEMAND</t>
+          <t>1155.1 - 1158.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1141.16 - 1182.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -731,39 +731,39 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,26 +772,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1402</v>
+        <v>8735</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>1401.0 - 1403.0 DR DEMAND</t>
+          <t>8544.05 - 8590.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>1442.0 - 1467.63 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -811,39 +811,39 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>ACUTAAS</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Acutaas Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>819.3</v>
+        <v>3210.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>800.2 - 804.9 DR DEMAND</t>
+          <t>3162.3 - 3190.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1545.87 - 1590.61 RD SUPPLY</t>
+          <t>1570.0 - 1704.9 DR DEMAND</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -891,12 +891,12 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Cholamandalam Investment and Finance Company Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,31 +932,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1170</v>
+        <v>1888.9</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>1155.1 - 1158.8 DR DEMAND</t>
+          <t>1862.0 - 1866.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1141.16 - 1182.0 DR DEMAND</t>
+          <t>1299.4 - 1354.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Larsen &amp; Toubro Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,26 +1012,26 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>8750</v>
+        <v>4081</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>8544.05 - 8590.0 DR DEMAND</t>
+          <t>4024.8 - 4041.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3256.29 - 3470.21 DR DEMAND</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1051,12 +1051,12 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>ACUTAAS</t>
+          <t>SBFC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Acutaas Chemicals Ltd.</t>
+          <t>SBFC Finance Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,26 +1092,26 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>3228.9</v>
+        <v>93.98999999999999</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>3162.3 - 3190.0 DR DEMAND</t>
+          <t>91.55 - 92.77 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1570.0 - 1704.9 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ASHOKLEY</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Cholamandalam Investment and Finance Company Ltd.</t>
+          <t>Ashok Leyland Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,26 +1172,26 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1873.5</v>
+        <v>173.8</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>1862.0 - 1866.2 DR DEMAND</t>
+          <t>169.75 - 171.64 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>1298.89 - 1354.17 DR DEMAND</t>
+          <t>96.04 - 98.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ANANDRATHI</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Anand Rathi Wealth Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,11 +1252,11 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2189.2</v>
+        <v>2020</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2167.9 - 2174.0 DR DEMAND</t>
+          <t>1970.9 - 1990.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -1266,12 +1266,12 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1710.6 - 1725.35 DR DEMAND</t>
+          <t>1427.1 - 1464.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1313,12 +1313,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>ASHOKLEY</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Ashok Leyland Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>173.1</v>
+        <v>717.05</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>169.75 - 171.64 DR DEMAND</t>
+          <t>705.5 - 709.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>96.04 - 98.98 DR DEMAND</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1393,17 +1393,17 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>HAL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Hindustan Aeronautics Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -1412,26 +1412,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>535.9</v>
+        <v>4998</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>533.65 - 534.95 DR DEMAND</t>
+          <t>4905.06 - 4935.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
+          <t>3004.72 - 3046.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1451,7 +1451,7 @@
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>TATACAP</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>Tata Capital Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,11 +1492,11 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2007.3</v>
+        <v>366.15</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>1970.9 - 1990.0 DR DEMAND</t>
+          <t>358.3 - 360.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1506,12 +1506,12 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1427.1 - 1464.22 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>GRAPHITE</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Graphite India Ltd.</t>
+          <t>Axis Bank Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>717.55</v>
+        <v>1251</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>705.5 - 709.95 DR DEMAND</t>
+          <t>1224.0 - 1235.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>551.99 - 610.0 DR DEMAND</t>
+          <t>1344.66 - 1399.02 RD SUPPLY</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="N15" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>HAL</t>
+          <t>BHARATFORG</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Hindustan Aeronautics Ltd.</t>
+          <t>Bharat Forge Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,28 +1652,28 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>5017</v>
+        <v>2062</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>4905.06 - 4935.0 DR DEMAND</t>
+          <t>2052.6 - 2057.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
+          <t>6.5 B</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>1605.33 - 1669.53 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>3004.72 - 3046.3 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>8.5 A</t>
-        </is>
-      </c>
       <c r="J16" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -1696,7 +1696,7 @@
       </c>
       <c r="N16" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>M&amp;MFIN</t>
+          <t>BHARTIARTL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Financial Services Ltd.</t>
+          <t>Bharti Airtel Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,26 +1732,26 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>389.6</v>
+        <v>1941.7</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>384.25 - 385.75 DR DEMAND</t>
+          <t>1901.3 - 1908.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1527.35 - 1537.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="M17" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N17" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Steel Authority of India Ltd.</t>
+          <t>Avenue Supermarts Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,31 +1812,31 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>172.75</v>
+        <v>3960</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>169.32 - 169.9 DR DEMAND</t>
+          <t>3885.5 - 3900.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>205.2 - 209.7 RD SUPPLY</t>
+          <t>3340.0 - 3403.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -1851,12 +1851,12 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>SONATSOFTW</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Sonata Software Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,26 +1892,26 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>307.8</v>
+        <v>1411.9</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>306.17 - 307.72 DR DEMAND</t>
+          <t>1401.0 - 1403.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1457.77 - 1476.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1931,12 +1931,12 @@
       </c>
       <c r="M19" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N19" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>TATACAP</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Tata Capital Ltd.</t>
+          <t>IndusInd Bank Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,26 +1972,26 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>365.55</v>
+        <v>1008</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>358.3 - 360.6 DR DEMAND</t>
+          <t>1002.5 - 1007.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>605.02 - 647.95 DR DEMAND</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="N20" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHARATFORG</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Bharat Forge Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,11 +2052,11 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>2069</v>
+        <v>8256</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2052.6 - 2057.8 DR DEMAND</t>
+          <t>8110.0 - 8151.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>1605.33 - 1669.53 DR DEMAND</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHARTIARTL</t>
+          <t>TORNTPOWER</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Bharti Airtel Ltd.</t>
+          <t>Torrent Power Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,31 +2132,31 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1922</v>
+        <v>1248.7</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>1901.3 - 1908.6 DR DEMAND</t>
+          <t>1226.7 - 1235.57 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>1527.35 - 1537.83 DR DEMAND</t>
+          <t>1186.52 - 1241.27 DR DEMAND</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>CGCL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Avenue Supermarts Ltd.</t>
+          <t>Capri Global Capital Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,31 +2212,31 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>3965</v>
+        <v>225.11</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>3885.5 - 3900.0 DR DEMAND</t>
+          <t>218.59 - 220.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>3340.0 - 3403.95 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2251,12 +2251,12 @@
       </c>
       <c r="M23" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N23" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>GRANULES</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>IndusInd Bank Ltd.</t>
+          <t>Granules India Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,26 +2292,26 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>1016.7</v>
+        <v>841.6</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>1002.5 - 1007.0 DR DEMAND</t>
+          <t>822.0 - 825.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>605.02 - 647.95 DR DEMAND</t>
+          <t>419.84 - 453.47 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
@@ -2331,12 +2331,12 @@
       </c>
       <c r="M24" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N24" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>HCLTECH</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Max Financial Services Ltd.</t>
+          <t>HCL Technologies Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,31 +2372,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1546.1</v>
+        <v>1318.4</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>1511.2 - 1533.0 DR DEMAND</t>
+          <t>1292.5 - 1298.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>950.0 - 998.1 DR DEMAND</t>
+          <t>1019.59 - 1059.19 DR DEMAND</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2411,12 +2411,12 @@
       </c>
       <c r="M25" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>NAVINFLUOR</t>
+          <t>HEXT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Navin Fluorine International Ltd.</t>
+          <t>Hexaware Technologies Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,26 +2452,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>8277.5</v>
+        <v>544.2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>8110.0 - 8151.0 DR DEMAND</t>
+          <t>532.0 - 536.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>4173.89 - 4245.43 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2491,12 +2491,12 @@
       </c>
       <c r="M26" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,12 +2513,12 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NETWEB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Netweb Technologies India Ltd.</t>
+          <t>MphasiS Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -2532,26 +2532,26 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>5065</v>
+        <v>2430</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4991.3 - 5007.2 DR DEMAND</t>
+          <t>2395.8 - 2415.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>3028.21 - 3096.87 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
@@ -2576,7 +2576,7 @@
       </c>
       <c r="N27" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>RECLTD</t>
+          <t>SHYAMMETL</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>REC Ltd.</t>
+          <t>Shyam Metalics and Energy Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,31 +2612,31 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>337</v>
+        <v>996.8</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>330.41 - 331.54 DR DEMAND</t>
+          <t>970.0 - 978.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>742.73 - 767.72 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="N28" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TORNTPOWER</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Torrent Power Ltd.</t>
+          <t>Yes Bank Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,11 +2692,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1243.7</v>
+        <v>22.74</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1226.7 - 1235.57 DR DEMAND</t>
+          <t>22.42 - 22.46 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2706,17 +2706,17 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>1186.52 - 1241.27 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K29" t="inlineStr">
@@ -2736,7 +2736,7 @@
       </c>
       <c r="N29" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>GRANULES</t>
+          <t>BAJAJHLDNG</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Granules India Ltd.</t>
+          <t>Bajaj Holdings &amp; Investment Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,26 +2772,26 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>841.15</v>
+        <v>11368</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>822.0 - 825.7 DR DEMAND</t>
+          <t>11219.0 - 11263.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>419.84 - 453.47 DR DEMAND</t>
+          <t>8482.6 - 8638.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
@@ -2801,7 +2801,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L30" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="M30" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>MphasiS Ltd.</t>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,31 +2852,31 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2424.5</v>
+        <v>561.95</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2395.8 - 2415.0 DR DEMAND</t>
+          <t>552.0 - 553.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>736.15 - 771.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K31" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SHYAMMETL</t>
+          <t>JSWENERGY</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Shyam Metalics and Energy Ltd.</t>
+          <t>JSW Energy Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,31 +2932,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>989.9</v>
+        <v>542</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>970.0 - 978.7 DR DEMAND</t>
+          <t>531.6 - 533.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>742.73 - 767.72 DR DEMAND</t>
+          <t>415.69 - 460.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Titagarh Rail Systems Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,26 +3012,26 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>831.75</v>
+        <v>1904</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>812.7 - 820.45 DR DEMAND</t>
+          <t>1868.3 - 1871.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
@@ -3051,12 +3051,12 @@
       </c>
       <c r="M33" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,12 +3073,12 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAJAJHLDNG</t>
+          <t>AIIL</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Bajaj Holdings &amp; Investment Ltd.</t>
+          <t>Authum Investment &amp; Infrastructure Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>11380</v>
+        <v>532.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>11219.0 - 11263.0 DR DEMAND</t>
+          <t>525.0 - 531.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>8482.6 - 8638.66 DR DEMAND</t>
+          <t>629.8 - 683.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3126,7 +3126,7 @@
       </c>
       <c r="L34" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M34" t="inlineStr">
@@ -3136,7 +3136,7 @@
       </c>
       <c r="N34" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>GMDCLTD</t>
+          <t>BAYERCROP</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Gujarat Mineral Development Corporation Ltd.</t>
+          <t>Bayer Cropscience Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,26 +3172,26 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>557.75</v>
+        <v>4066.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>552.0 - 553.8 DR DEMAND</t>
+          <t>4030.0 - 4045.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>736.15 - 771.9 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I35" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J35" t="inlineStr">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>IRCTC</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,26 +3252,26 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>488.35</v>
+        <v>433.95</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>485.3 - 485.95 DR DEMAND</t>
+          <t>430.45 - 433.07 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J36" t="inlineStr">
@@ -3281,7 +3281,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>JSWENERGY</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JSW Energy Ltd.</t>
+          <t>GMR Airports Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,26 +3332,26 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>543.95</v>
+        <v>100.41</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>531.6 - 533.45 DR DEMAND</t>
+          <t>99.9 - 100.32 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>415.69 - 460.71 DR DEMAND</t>
+          <t>112.74 - 115.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="I37" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J37" t="inlineStr">
@@ -3371,12 +3371,12 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>MEDANTA</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Global Health Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>3540.9</v>
+        <v>1408.2</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>3460.0 - 3476.8 DR DEMAND</t>
+          <t>1382.71 - 1393.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>2976.44 - 3086.89 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3441,7 +3441,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L38" t="inlineStr">
@@ -3456,7 +3456,7 @@
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>NAVA</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>Nava Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,31 +3492,31 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1900</v>
+        <v>556.75</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>1868.3 - 1871.0 DR DEMAND</t>
+          <t>545.15 - 549.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>497.01 - 517.17 DR DEMAND</t>
         </is>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J39" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K39" t="inlineStr">
@@ -3531,12 +3531,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BAYERCROP</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Bayer Cropscience Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,11 +3572,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4069.9</v>
+        <v>272.05</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>4030.0 - 4045.8 DR DEMAND</t>
+          <t>263.3 - 267.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>217.6 - 220.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3633,17 +3633,17 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>CANFINHOME</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Can Fin Homes Ltd.</t>
+          <t>NMDC Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D41" t="inlineStr">
@@ -3652,11 +3652,11 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>817.65</v>
+        <v>83.95</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>807.0 - 814.35 DR DEMAND</t>
+          <t>81.77 - 82.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -3666,12 +3666,12 @@
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>545.13 - 563.82 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>TATAPOWER</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Tata Power Co. Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>434.85</v>
+        <v>375.25</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>430.45 - 433.07 DR DEMAND</t>
+          <t>367.85 - 371.35 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>322.44 - 334.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,26 +3812,26 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>497</v>
+        <v>580.05</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>458.9 - 460.7 DR DEMAND</t>
+          <t>561.05 - 569.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>458.9 - 495.25 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>ABFRL</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>NMDC Ltd.</t>
+          <t>Aditya Birla Fashion and Retail Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,16 +3892,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>83.34999999999999</v>
+        <v>54.75</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>81.77 - 82.35 DR DEMAND</t>
+          <t>53.51 - 53.89 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>ONESOURCE</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Onesource Specialty Pharma Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,36 +3972,36 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1520.5</v>
+        <v>1095</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>1479.1 - 1501.3 DR DEMAND</t>
+          <t>1070.8 - 1078.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>783.09 - 796.65 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J45" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,17 +4033,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>CESC</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Polycab India Ltd.</t>
+          <t>CESC Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D46" t="inlineStr">
@@ -4052,36 +4052,36 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>9140</v>
+        <v>156.61</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>9025.0 - 9125.0 DR DEMAND</t>
+          <t>154.67 - 155.21 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>6631.53 - 6768.39 DR DEMAND</t>
+          <t>133.19 - 139.44 DR DEMAND</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,36 +4132,36 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>568</v>
+        <v>1278</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>557.75 - 559.63 DR DEMAND</t>
+          <t>1256.9 - 1260.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>557.75 - 565.72 DR DEMAND</t>
+          <t>1390.17 - 1435.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L47" t="inlineStr">
@@ -4171,12 +4171,12 @@
       </c>
       <c r="M47" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>ABFRL</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Aditya Birla Fashion and Retail Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>54.47</v>
+        <v>321.7</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>53.51 - 53.89 DR DEMAND</t>
+          <t>317.0 - 317.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>349.75 - 398.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4251,7 +4251,7 @@
       </c>
       <c r="M48" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N48" t="inlineStr">
@@ -4273,12 +4273,12 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bajaj Finance Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -4292,31 +4292,31 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>1080.2</v>
+        <v>749.25</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>1070.8 - 1078.0 DR DEMAND</t>
+          <t>737.82 - 743.27 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>783.09 - 796.65 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>TRIDENT</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Trident Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,26 +4372,26 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>754.3</v>
+        <v>24.63</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>737.82 - 743.27 DR DEMAND</t>
+          <t>24.14 - 24.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
@@ -4401,7 +4401,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4411,7 +4411,7 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>HSCL</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Himadri Speciality Chemical Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,11 +4452,11 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>750.25</v>
+        <v>495.65</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>736.0 - 749.65 DR DEMAND</t>
+          <t>482.38 - 486.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
@@ -4466,7 +4466,7 @@
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>417.93 - 437.01 DR DEMAND</t>
+          <t>274.28 - 291.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
@@ -4481,12 +4481,12 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4513,12 +4513,12 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>BAJAJ-AUTO</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>Bajaj Auto Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -4532,26 +4532,26 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3415</v>
+        <v>11793</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3384.6 - 3401.0 DR DEMAND</t>
+          <t>11541.0 - 11600.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>9501.0 - 9716.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4593,17 +4593,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>CHOLAHLDNG</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>Cholamandalam Financial Holdings Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>1068</v>
+        <v>1574.2</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>1054.3 - 1061.9 DR DEMAND</t>
+          <t>1540.48 - 1544.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>998.75 - 1006.29 DR DEMAND</t>
+          <t>1358.29 - 1396.78 DR DEMAND</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,17 +4673,17 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>HINDUNILVR</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>Hindustan Unilever Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
@@ -4692,16 +4692,16 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>24.49</v>
+        <v>2028</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>24.14 - 24.3 DR DEMAND</t>
+          <t>2016.0 - 2022.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="K54" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L54" t="inlineStr">
@@ -4731,12 +4731,12 @@
       </c>
       <c r="M54" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>BAJAJ-AUTO</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Bajaj Auto Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,36 +4772,36 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>11645</v>
+        <v>125.13</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>11541.0 - 11600.0 DR DEMAND</t>
+          <t>122.35 - 124.18 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>9501.0 - 9716.0 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>CHOLAHLDNG</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Cholamandalam Financial Holdings Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,36 +4852,36 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>1557.3</v>
+        <v>3424.8</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>1540.48 - 1544.68 DR DEMAND</t>
+          <t>3384.6 - 3401.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>1358.29 - 1396.78 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K56" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L56" t="inlineStr">
@@ -4913,12 +4913,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EIHOTEL</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>EIH Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4932,11 +4932,11 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>297.65</v>
+        <v>602.05</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>282.42 - 283.71 DR DEMAND</t>
+          <t>594.25 - 600.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -4946,22 +4946,22 @@
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>282.42 - 293.67 DR DEMAND</t>
+          <t>811.74 - 836.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ELECON</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Elecon Engineering Co. Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,26 +5012,26 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>428.85</v>
+        <v>1782</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>425.2 - 428.0 DR DEMAND</t>
+          <t>1700.4 - 1706.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
           <t>4.5 C</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>630.8 - 668.52 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>4.0 C</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
@@ -5073,17 +5073,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,11 +5092,11 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5193</v>
+        <v>1107.7</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>5137.5 - 5171.0 DR DEMAND</t>
+          <t>1094.12 - 1098.81 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
@@ -5106,12 +5106,12 @@
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>3773.62 - 4043.17 DR DEMAND</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>IDBI</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>PG Electroplast Ltd.</t>
+          <t>IDBI Bank Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,21 +5172,21 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>601.9</v>
+        <v>81.73999999999999</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>594.25 - 600.1 DR DEMAND</t>
+          <t>80.17 - 80.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>811.74 - 836.08 RD SUPPLY</t>
+          <t>116.01 - 117.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
@@ -5196,7 +5196,7 @@
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,12 +5233,12 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Indian Energy Exchange Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1780.4</v>
+        <v>123.35</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1700.4 - 1706.0 DR DEMAND</t>
+          <t>120.91 - 122.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SIGNATURE</t>
+          <t>RHIM</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Signatureglobal (India) Ltd.</t>
+          <t>RHI MAGNESITA INDIA LTD.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,26 +5332,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>784.9</v>
+        <v>374.75</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>758.0 - 769.55 DR DEMAND</t>
+          <t>366.95 - 370.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>989.8 - 1111.0 RD SUPPLY</t>
+          <t>323.05 - 337.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Zydus Lifesciences Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,21 +5412,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>1104.5</v>
+        <v>985.45</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>1094.12 - 1098.81 DR DEMAND</t>
+          <t>1085.3 - 1092.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>855.18 - 875.51 DR DEMAND</t>
+          <t>870.0 - 974.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
@@ -5436,7 +5436,7 @@
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>IDBI</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>IDBI Bank Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>80.72</v>
+        <v>571.9</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>80.17 - 80.53 DR DEMAND</t>
+          <t>557.75 - 559.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
+          <t>3.5 C</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>557.75 - 565.72 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
           <t>4.0 C</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr">
-        <is>
-          <t>116.01 - 117.55 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr">
-        <is>
-          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5553,17 +5553,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Indian Energy Exchange Ltd.</t>
+          <t>Voltas Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5572,26 +5572,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>123</v>
+        <v>1219.5</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>120.91 - 122.0 DR DEMAND</t>
+          <t>1194.85 - 1201.92 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1425.92 - 1533.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5611,7 +5611,7 @@
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
@@ -5633,17 +5633,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RHI MAGNESITA INDIA LTD.</t>
+          <t>Bank of Baroda</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,26 +5652,26 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>374.9</v>
+        <v>244.5</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>366.95 - 370.0 DR DEMAND</t>
+          <t>239.0 - 240.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>323.05 - 337.85 DR DEMAND</t>
+          <t>178.57 - 184.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
@@ -5681,7 +5681,7 @@
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5696,7 +5696,7 @@
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
@@ -5713,17 +5713,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>SCHAEFFLER</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Schaeffler India Ltd.</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,11 +5732,11 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>4104.9</v>
+        <v>906.95</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>4025.0 - 4035.0 DR DEMAND</t>
+          <t>901.59 - 906.13 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -5746,17 +5746,17 @@
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>3489.69 - 3548.8 DR DEMAND</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K67" t="inlineStr">
@@ -5776,7 +5776,7 @@
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
@@ -5793,17 +5793,17 @@
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>SCHAEFFLER</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Voltas Ltd.</t>
+          <t>Schaeffler India Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,26 +5812,26 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1223</v>
+        <v>4049.3</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1194.85 - 1201.92 DR DEMAND</t>
+          <t>4025.0 - 4035.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>1425.92 - 1533.08 RD SUPPLY</t>
+          <t>3489.69 - 3548.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
@@ -5851,12 +5851,12 @@
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
@@ -5873,17 +5873,17 @@
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Bank of Baroda</t>
+          <t>Waaree Energies Ltd.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,11 +5892,11 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>245</v>
+        <v>2675</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>239.0 - 240.45 DR DEMAND</t>
+          <t>2656.9 - 2660.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -5906,12 +5906,12 @@
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>178.57 - 184.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -5953,17 +5953,17 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>ECLERX</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>eClerx Services Ltd.</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,31 +5972,31 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1832.9</v>
+        <v>685.7</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>1735.0 - 1811.7 DR DEMAND</t>
+          <t>675.15 - 678.96 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>1083.73 - 1257.24 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K70" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
@@ -6033,17 +6033,17 @@
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Waaree Energies Ltd.</t>
+          <t>Tata Steel Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
@@ -6052,26 +6052,26 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>2679</v>
+        <v>183.5</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2656.9 - 2660.9 DR DEMAND</t>
+          <t>182.01 - 182.63 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>156.83 - 164.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
@@ -6096,7 +6096,7 @@
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
@@ -6113,17 +6113,17 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Eris Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
@@ -6132,26 +6132,26 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>184</v>
+        <v>1326</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>1315.44 - 1323.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,7 +6161,7 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
@@ -6171,12 +6171,12 @@
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6193,17 +6193,17 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>IRCTC</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Indian Bank</t>
+          <t>Indian Railway Catering And Tourism Corporation Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6212,36 +6212,36 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>873.15</v>
+        <v>485.9</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>873.1 - 875.6 DR DEMAND</t>
+          <t>485.3 - 485.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>748.11 - 819.79 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6292,7 +6292,7 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1650</v>
+        <v>1660</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
@@ -6372,7 +6372,7 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>216.94</v>
+        <v>218.44</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -6433,17 +6433,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>ERIS</t>
+          <t>WHIRLPOOL</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Eris Lifesciences Ltd.</t>
+          <t>Whirlpool of India Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D76" t="inlineStr">
@@ -6452,11 +6452,11 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1348.3</v>
+        <v>775.75</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>1346.0 - 1353.0 DR DEMAND</t>
+          <t>751.0 - 753.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
@@ -6466,12 +6466,12 @@
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>771.0 - 789.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
@@ -6513,17 +6513,17 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>INDIACEM</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>India Cements Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
@@ -6532,26 +6532,26 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>369.7</v>
+        <v>1056.3</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>366.25 - 371.8 DR DEMAND</t>
+          <t>1054.3 - 1061.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>400.0 - 416.4 RD SUPPLY</t>
+          <t>998.75 - 1006.29 DR DEMAND</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J77" t="inlineStr">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6593,17 +6593,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,11 +6612,11 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>123.66</v>
+        <v>5165</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>122.35 - 124.18 DR DEMAND</t>
+          <t>5137.5 - 5171.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -6626,17 +6626,17 @@
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3773.62 - 4043.17 DR DEMAND</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K78" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="M78" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N78" t="inlineStr">
@@ -6692,7 +6692,7 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>598.05</v>
+        <v>595.45</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>ASIANPAINT</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Asian Paints Ltd.</t>
+          <t>Adani Green Energy Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,11 +6772,11 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2630.8</v>
+        <v>1301.8</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2624.0 - 2635.7 DR DEMAND</t>
+          <t>1291.4 - 1302.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>2083.96 - 2137.91 DR DEMAND</t>
+          <t>765.0 - 814.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="J80" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K80" t="inlineStr">
@@ -6811,7 +6811,7 @@
       </c>
       <c r="M80" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>OLECTRA</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,11 +6852,11 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>1305.6</v>
+        <v>2625.2</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>1297.2 - 1305.9 DR DEMAND</t>
+          <t>2624.0 - 2635.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
@@ -6866,17 +6866,17 @@
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>1508.5 - 1556.0 RD SUPPLY</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
@@ -6913,17 +6913,17 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>SUNTV</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Sun TV Network Ltd.</t>
+          <t>Polycab India Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
@@ -6932,36 +6932,36 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>480.9</v>
+        <v>9125</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>529.67 - 537.44 RD SUPPLY</t>
+          <t>9025.0 - 9125.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>472.32 - 532.12 DR DEMAND</t>
+          <t>6631.53 - 6768.39 DR DEMAND</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
@@ -6993,17 +6993,17 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>LINDEINDIA</t>
+          <t>SUNTV</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Linde India Ltd.</t>
+          <t>Sun TV Network Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,26 +7012,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6702.5</v>
+        <v>477.55</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>6546.9 - 6753.55 DR DEMAND</t>
+          <t>529.67 - 537.44 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>7487.35 - 7842.09 RD SUPPLY</t>
+          <t>472.32 - 532.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7051,12 +7051,12 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,17 +7073,17 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>ASTERDM</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Aster DM Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D84" t="inlineStr">
@@ -7092,26 +7092,26 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>902.2</v>
+        <v>765.65</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>901.59 - 906.13 DR DEMAND</t>
+          <t>761.6 - 765.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>516.84 - 549.74 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J84" t="inlineStr">
@@ -7121,22 +7121,22 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M84" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,17 +7153,17 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>ECLERX</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Ltd.</t>
+          <t>eClerx Services Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
@@ -7172,31 +7172,31 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>678.45</v>
+        <v>1804.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>675.15 - 678.96 DR DEMAND</t>
+          <t>1735.0 - 1811.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1083.73 - 1257.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K85" t="inlineStr">
@@ -7216,7 +7216,7 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
@@ -7233,55 +7233,55 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>LINDEINDIA</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Eicher Motors Ltd.</t>
+          <t>Linde India Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>7990.5</v>
+        <v>6695</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>8134.81 - 8144.71 RD SUPPLY</t>
+          <t>6546.9 - 6753.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>7927.48 - 8144.71 RD SUPPLY</t>
+          <t>7487.35 - 7842.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7291,67 +7291,67 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>INDIACEM</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>India Cements Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>26405</v>
+        <v>370.65</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>25527.65 - 25600.93 DR DEMAND</t>
+          <t>366.25 - 371.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>26475.47 - 27633.38 RD SUPPLY</t>
+          <t>400.0 - 416.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7371,39 +7371,39 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>Eicher Motors Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
@@ -7412,36 +7412,36 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5382.5</v>
+        <v>8042</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>5475.0 - 5510.0 RD SUPPLY</t>
+          <t>8134.81 - 8144.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>5806.11 - 5871.99 RD SUPPLY</t>
+          <t>7927.48 - 8144.71 RD SUPPLY</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7456,7 +7456,7 @@
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
@@ -7473,17 +7473,17 @@
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>ANURAS</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Anupam Rasayan India Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
@@ -7492,11 +7492,11 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>1225.4</v>
+        <v>5400</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>1249.6 - 1259.9 RD SUPPLY</t>
+          <t>5475.0 - 5510.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
@@ -7506,7 +7506,7 @@
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>600.61 - 631.99 DR DEMAND</t>
+          <t>5806.11 - 5871.99 RD SUPPLY</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
@@ -7526,7 +7526,7 @@
       </c>
       <c r="L89" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M89" t="inlineStr">
@@ -7553,17 +7553,17 @@
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>ANURAS</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Trent Ltd.</t>
+          <t>Anupam Rasayan India Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,11 +7572,11 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>2953</v>
+        <v>1239.4</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2989.9 - 3020.6 RD SUPPLY</t>
+          <t>1249.6 - 1259.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
@@ -7586,12 +7586,12 @@
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>3285.0 - 3399.7 RD SUPPLY</t>
+          <t>600.61 - 631.99 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J90" t="inlineStr">
@@ -7652,7 +7652,7 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>7250</v>
+        <v>7275</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>ATGL</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Axis Bank Ltd.</t>
+          <t>Adani Total Gas Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,11 +7732,11 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>1235</v>
+        <v>657.65</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>1247.3 - 1250.0 RD SUPPLY</t>
+          <t>666.5 - 687.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>1344.66 - 1399.02 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,11 +7812,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>263.5</v>
+        <v>150.55</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>268.0 - 268.95 RD SUPPLY</t>
+          <t>151.0 - 153.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>239.47 - 242.91 DR DEMAND</t>
+          <t>141.74 - 145.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7873,17 +7873,17 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D94" t="inlineStr">
@@ -7892,11 +7892,11 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>2578.6</v>
+        <v>264.8</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>2630.0 - 2644.7 RD SUPPLY</t>
+          <t>268.0 - 268.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
@@ -7906,12 +7906,12 @@
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>3066.4 - 3131.26 RD SUPPLY</t>
+          <t>239.47 - 242.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
@@ -7953,17 +7953,17 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Adani Enterprises Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D95" t="inlineStr">
@@ -7972,31 +7972,31 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>431.85</v>
+        <v>2994.9</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>439.3 - 443.3 RD SUPPLY</t>
+          <t>3049.0 - 3058.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>520.87 - 531.92 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K95" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Adani Enterprises Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,11 +8052,11 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2990.3</v>
+        <v>692.35</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>3049.0 - 3058.6 RD SUPPLY</t>
+          <t>700.0 - 701.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -8086,7 +8086,7 @@
       </c>
       <c r="L96" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M96" t="inlineStr">
@@ -8113,12 +8113,12 @@
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>IIFL</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>IIFL Finance Ltd.</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
@@ -8132,31 +8132,31 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>536.3</v>
+        <v>636.7</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>543.0 - 544.3 RD SUPPLY</t>
+          <t>648.2 - 649.64 RD SUPPLY</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I97" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J97" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K97" t="inlineStr">
@@ -8193,17 +8193,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D98" t="inlineStr">
@@ -8212,36 +8212,36 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>148.95</v>
+        <v>1925</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>151.37 - 152.17 RD SUPPLY</t>
+          <t>1939.5 - 1950.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
+          <t>1853.5 - 1993.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I98" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J98" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K98" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Lupin Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,31 +8292,31 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>2225</v>
+        <v>3650</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>2259.0 - 2266.0 RD SUPPLY</t>
+          <t>3713.74 - 3719.99 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>1834.7 - 1878.61 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Marico Ltd.</t>
+          <t>Trent Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,11 +8372,11 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>850</v>
+        <v>2970</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>865.2 - 867.35 RD SUPPLY</t>
+          <t>2989.9 - 3020.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -8386,12 +8386,12 @@
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>705.08 - 721.7 DR DEMAND</t>
+          <t>7108.74 - 7477.68 RD SUPPLY</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8433,17 +8433,17 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>DIXON</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Phoenix Mills Ltd.</t>
+          <t>Dixon Technologies (India) Ltd.</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D101" t="inlineStr">
@@ -8452,26 +8452,26 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>1919</v>
+        <v>14850</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>1939.5 - 1950.0 RD SUPPLY</t>
+          <t>14860.0 - 14890.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>1853.5 - 1993.0 RD SUPPLY</t>
+          <t>16444.68 - 17061.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I101" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J101" t="inlineStr">
@@ -8481,12 +8481,12 @@
       </c>
       <c r="K101" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L101" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>7.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>CLEAN</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Yes Bank Ltd.</t>
+          <t>Clean Science and Technology Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,26 +8532,26 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>22.74</v>
+        <v>834.7</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>22.92 - 23.02 RD SUPPLY</t>
+          <t>842.0 - 843.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1545.87 - 1590.61 RD SUPPLY</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
@@ -8576,7 +8576,7 @@
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>7.5 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O102" t="inlineStr">
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>IDEA</t>
+          <t>CANHLIFE</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Vodafone Idea Ltd.</t>
+          <t>Canara HSBC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,26 +8612,26 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>14.07</v>
+        <v>151.69</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>14.11 - 14.19 RD SUPPLY</t>
+          <t>151.78 - 152.79 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>12.6 - 13.01 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8656,7 +8656,7 @@
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KOTAKBANK</t>
+          <t>EIDPARRY</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Kotak Mahindra Bank Ltd.</t>
+          <t>E.I.D. Parry (India) Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,41 +8692,41 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>390.25</v>
+        <v>810.25</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>392.7 - 396.35 RD SUPPLY</t>
+          <t>824.05 - 828.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>431.46 - 447.25 RD SUPPLY</t>
+          <t>639.0 - 660.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M104" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>HDFCAMC</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>HDFC Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,26 +8772,26 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>1417.2</v>
+        <v>2624</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>1442.9 - 1447.0 RD SUPPLY</t>
+          <t>2729.2 - 2767.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>2640.84 - 2839.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
@@ -8801,7 +8801,7 @@
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8816,7 +8816,7 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,36 +8852,36 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>1461.8</v>
+        <v>542</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>1478.5 - 1485.2 RD SUPPLY</t>
+          <t>543.0 - 544.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>6.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O106" t="inlineStr">
@@ -8913,17 +8913,17 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>CANHLIFE</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Canara HSBC Life Insurance Company Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>151.63</v>
+        <v>507.3</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>151.78 - 152.79 RD SUPPLY</t>
+          <t>511.5 - 512.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>699.84 - 715.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>Kaynes Technology India Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>188.75</v>
+        <v>3815</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>189.0 - 190.45 RD SUPPLY</t>
+          <t>3832.0 - 3860.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>4044.4 - 4538.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9073,17 +9073,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>GRSE</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Garden Reach Shipbuilders &amp; Engineers Ltd.</t>
+          <t>Max Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,21 +9092,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>2638.3</v>
+        <v>1575</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2689.0 - 2706.0 RD SUPPLY</t>
+          <t>1584.5 - 1587.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>1176.64 - 1247.24 DR DEMAND</t>
+          <t>950.0 - 998.1 DR DEMAND</t>
         </is>
       </c>
       <c r="I109" t="inlineStr">
@@ -9116,12 +9116,12 @@
       </c>
       <c r="J109" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K109" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>JUBLINGREA</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Jubilant Ingrevia Ltd.</t>
+          <t>National Aluminium Co. Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,11 +9172,11 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>708.4</v>
+        <v>385.6</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>538.29 - 548.2 DR DEMAND</t>
+          <t>392.0 - 395.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>711.35 - 766.92 RD SUPPLY</t>
+          <t>131.8 - 149.71 DR DEMAND</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>PARADEEP</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kaynes Technology India Ltd.</t>
+          <t>Paradeep Phosphates Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,11 +9252,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>3823.3</v>
+        <v>148.64</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>3832.0 - 3860.0 RD SUPPLY</t>
+          <t>151.0 - 152.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9266,7 +9266,7 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>4044.4 - 4538.6 RD SUPPLY</t>
+          <t>82.87 - 86.49 DR DEMAND</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,26 +9332,26 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>429.5</v>
+        <v>184.68</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>430.02 - 431.11 RD SUPPLY</t>
+          <t>187.93 - 189.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>429.62 - 438.85 RD SUPPLY</t>
+          <t>196.47 - 199.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
@@ -9361,7 +9361,7 @@
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Petronet LNG Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,41 +9412,41 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>288.15</v>
+        <v>438.3</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>288.45 - 290.4 RD SUPPLY</t>
+          <t>439.3 - 443.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>520.87 - 531.92 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H113" t="inlineStr">
-        <is>
-          <t>232.67 - 245.62 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>6.0 B</t>
-        </is>
-      </c>
       <c r="J113" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K113" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L113" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>BRIGADE</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Brigade Enterprises Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,26 +9492,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>587.7</v>
+        <v>85.84</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>495.04 - 501.02 DR DEMAND</t>
+          <t>86.55 - 86.67 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>590.46 - 609.89 RD SUPPLY</t>
+          <t>57.91 - 58.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>CDSL</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Central Depository Services (India) Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,11 +9572,11 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1329</v>
+        <v>1453.5</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>1350.0 - 1362.0 RD SUPPLY</t>
+          <t>1478.5 - 1485.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9586,12 +9586,12 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1730.38 - 1955.87 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>KFINTECH</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>IDFC First Bank Ltd.</t>
+          <t>Kfin Technologies Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,26 +9652,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>85.48999999999999</v>
+        <v>961</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>86.55 - 86.67 RD SUPPLY</t>
+          <t>974.0 - 982.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>57.91 - 58.68 DR DEMAND</t>
+          <t>1329.97 - 1360.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9681,7 +9681,7 @@
       </c>
       <c r="K116" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>TATAINVEST</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>AU Small Finance Bank Ltd.</t>
+          <t>Tata Investment Corporation Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,31 +9732,31 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1075</v>
+        <v>649.35</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1087.6 - 1105.9 RD SUPPLY</t>
+          <t>691.04 - 711.33 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>830.84 - 841.88 DR DEMAND</t>
+          <t>655.32 - 737.89 RD SUPPLY</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K117" t="inlineStr">
@@ -9793,17 +9793,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,36 +9812,36 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>14462</v>
+        <v>31.07</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>14589.0 - 14614.0 RD SUPPLY</t>
+          <t>31.46 - 31.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>16444.68 - 17061.41 RD SUPPLY</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J118" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K118" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L118" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="N118" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O118" t="inlineStr">
@@ -9873,12 +9873,12 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Eternal Ltd.</t>
+          <t>Devyani International Ltd.</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
@@ -9892,26 +9892,26 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>320</v>
+        <v>147.79</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>322.6 - 323.6 RD SUPPLY</t>
+          <t>137.35 - 138.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>194.8 - 201.7 DR DEMAND</t>
+          <t>148.0 - 159.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9953,17 +9953,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>TATAINVEST</t>
+          <t>IDEA</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Tata Investment Corporation Ltd.</t>
+          <t>Vodafone Idea Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,31 +9972,31 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>652.9</v>
+        <v>14.03</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>691.04 - 711.33 RD SUPPLY</t>
+          <t>14.11 - 14.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>655.32 - 737.89 RD SUPPLY</t>
+          <t>12.6 - 13.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K120" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>ANTHEM</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Anthem Biosciences Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,26 +10052,26 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>881.9</v>
+        <v>1904.7</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>898.0 - 899.9 RD SUPPLY</t>
+          <t>1950.4 - 1960.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
+          <t>8.0 A</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>1905.52 - 1995.18 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
           <t>4.5 C</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>—</t>
         </is>
       </c>
       <c r="J121" t="inlineStr">
@@ -10113,17 +10113,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>OFSS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Oracle Financial Services Software Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,21 +10132,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>1349</v>
+        <v>11826</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>1232.5 - 1240.0 DR DEMAND</t>
+          <t>11318.0 - 11420.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>1364.1 - 1481.2 RD SUPPLY</t>
+          <t>11863.13 - 12262.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -10193,17 +10193,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Ramkrishna Forgings Ltd.</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10212,36 +10212,36 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>30.91</v>
+        <v>745.4</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>31.46 - 31.6 RD SUPPLY</t>
+          <t>755.8 - 761.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>459.41 - 465.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10273,17 +10273,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>ITI</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>ITI Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10292,41 +10292,41 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>279.95</v>
+        <v>1048</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>285.65 - 288.0 RD SUPPLY</t>
+          <t>1007.4 - 1015.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1049.53 - 1101.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10353,17 +10353,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Jindal Steel Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10372,36 +10372,36 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>1115</v>
+        <v>1128.2</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>1124.0 - 1126.8 RD SUPPLY</t>
+          <t>1141.0 - 1153.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>1244.2 - 1272.1 RD SUPPLY</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>TITAGARH</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Motilal Oswal Financial Services Ltd.</t>
+          <t>Titagarh Rail Systems Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,26 +10452,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>942.1</v>
+        <v>849.3</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>829.0 - 831.6 DR DEMAND</t>
+          <t>850.75 - 869.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>952.5 - 989.75 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10513,17 +10513,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>BRITANNIA</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>Britannia Industries Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10532,26 +10532,26 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>1869.7</v>
+        <v>5548</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>1950.4 - 1960.7 RD SUPPLY</t>
+          <t>5777.77 - 5826.96 RD SUPPLY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>1905.52 - 1995.18 RD SUPPLY</t>
+          <t>5632.2 - 5826.96 RD SUPPLY</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10593,17 +10593,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>OFSS</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Oracle Financial Services Software Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10612,26 +10612,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>11774</v>
+        <v>188.57</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>11318.0 - 11420.0 DR DEMAND</t>
+          <t>189.0 - 190.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>11863.13 - 12262.5 RD SUPPLY</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10673,17 +10673,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>MAHABANK</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>Bank of Maharashtra</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10692,26 +10692,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>749.2</v>
+        <v>80.28</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>755.8 - 761.8 RD SUPPLY</t>
+          <t>81.75 - 82.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>459.41 - 465.85 DR DEMAND</t>
+          <t>91.75 - 94.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10721,7 +10721,7 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
@@ -10736,7 +10736,7 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
@@ -10753,17 +10753,17 @@
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10772,28 +10772,28 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>1048.6</v>
+        <v>743.3</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>1007.4 - 1015.3 DR DEMAND</t>
+          <t>743.51 - 757.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>451.85 - 473.12 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="H130" t="inlineStr">
-        <is>
-          <t>1049.53 - 1101.1 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>4.5 C</t>
-        </is>
-      </c>
       <c r="J130" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -10816,7 +10816,7 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
@@ -10833,17 +10833,17 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>CARTRADE</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Cartrade Tech Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D131" t="inlineStr">
@@ -10852,26 +10852,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>413.1</v>
+        <v>2895.2</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>452.84 - 457.74 RD SUPPLY</t>
+          <t>2915.0 - 3081.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>414.97 - 443.6 RD SUPPLY</t>
+          <t>1485.0 - 1525.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10896,7 +10896,7 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
@@ -10913,17 +10913,17 @@
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MINDACORP</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Minda Corporation Ltd.</t>
+          <t>Coforge Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D132" t="inlineStr">
@@ -10932,26 +10932,26 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>738.9</v>
+        <v>1882</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>743.51 - 757.85 RD SUPPLY</t>
+          <t>1762.2 - 1773.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>451.85 - 473.12 DR DEMAND</t>
+          <t>1906.98 - 1973.26 RD SUPPLY</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
@@ -10961,7 +10961,7 @@
       </c>
       <c r="K132" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L132" t="inlineStr">
@@ -10976,7 +10976,7 @@
       </c>
       <c r="N132" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O132" t="inlineStr">
@@ -10993,17 +10993,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>Jindal Steel Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11012,26 +11012,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>1200.9</v>
+        <v>1118.9</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>1130.0 - 1135.0 DR DEMAND</t>
+          <t>1124.0 - 1126.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
+          <t>1244.2 - 1272.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11041,7 +11041,7 @@
       </c>
       <c r="K133" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L133" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11073,17 +11073,17 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>URBANCO</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Urban Company Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D134" t="inlineStr">
@@ -11092,36 +11092,36 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>147.83</v>
+        <v>1313.2</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>148.47 - 152.21 RD SUPPLY</t>
+          <t>1328.9 - 1344.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1424.22 - 1466.62 RD SUPPLY</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L134" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11153,17 +11153,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>CDSL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Central Depository Services (India) Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11172,36 +11172,36 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>1311</v>
+        <v>1345.9</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>1328.9 - 1344.9 RD SUPPLY</t>
+          <t>1350.0 - 1362.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>1424.22 - 1466.62 RD SUPPLY</t>
+          <t>1730.38 - 1955.87 RD SUPPLY</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K135" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L135" t="inlineStr">
@@ -11216,7 +11216,7 @@
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
@@ -11233,17 +11233,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>NIACL</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>The New India Assurance Company Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11252,11 +11252,11 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>650.8</v>
+        <v>183.08</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>658.7 - 664.95 RD SUPPLY</t>
+          <t>183.76 - 189.37 RD SUPPLY</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>415.9 - 440.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11313,17 +11313,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>360ONE</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>360 ONE WAM Ltd.</t>
+          <t>Petronet LNG Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11332,26 +11332,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1180.5</v>
+        <v>291.4</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1047.7 - 1054.9 DR DEMAND</t>
+          <t>293.32 - 298.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1185.06 - 1260.04 RD SUPPLY</t>
+          <t>232.67 - 245.62 DR DEMAND</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11361,7 +11361,7 @@
       </c>
       <c r="K137" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L137" t="inlineStr">
@@ -11376,7 +11376,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O137" t="inlineStr">
@@ -11412,7 +11412,7 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>7430</v>
+        <v>7479</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
@@ -11473,17 +11473,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>AEGISLOG</t>
+          <t>CREDITACC</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Aegis Logistics Ltd.</t>
+          <t>CreditAccess Grameen Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11492,11 +11492,11 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>1364</v>
+        <v>1534.5</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>1383.9 - 1434.5 RD SUPPLY</t>
+          <t>1547.0 - 1559.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
@@ -11521,7 +11521,7 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
@@ -11553,17 +11553,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>CREDITACC</t>
+          <t>TBOTEK</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>CreditAccess Grameen Ltd.</t>
+          <t>TBO Tek Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11572,11 +11572,11 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1519.4</v>
+        <v>1702.6</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1547.0 - 1559.4 RD SUPPLY</t>
+          <t>1710.0 - 1734.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
@@ -11586,7 +11586,7 @@
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1602.0 - 1634.0 RD SUPPLY</t>
+          <t>1004.2 - 1057.3 DR DEMAND</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
@@ -11633,17 +11633,17 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>ELECON</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Elecon Engineering Co. Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
@@ -11652,11 +11652,11 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>152.64</v>
+        <v>451.7</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>151.0 - 153.0 RD SUPPLY</t>
+          <t>450.65 - 452.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
@@ -11666,12 +11666,12 @@
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>630.8 - 668.52 RD SUPPLY</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11686,7 +11686,7 @@
       </c>
       <c r="L141" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M141" t="inlineStr">
@@ -11732,7 +11732,7 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>823.5</v>
+        <v>821.9</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
@@ -11812,7 +11812,7 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2571</v>
+        <v>2529.7</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
@@ -11873,17 +11873,17 @@
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
         <is>
-          <t>Persistent Systems Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D144" t="inlineStr">
@@ -11892,26 +11892,26 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5510</v>
+        <v>348.1</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>4947.91 - 4956.88 DR DEMAND</t>
+          <t>346.0 - 350.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>5219.87 - 5592.58 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I144" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J144" t="inlineStr">
@@ -11936,7 +11936,7 @@
       </c>
       <c r="N144" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>6.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O144" t="inlineStr">
@@ -11972,7 +11972,7 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>16615</v>
+        <v>16784</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
@@ -12052,7 +12052,7 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>2012</v>
+        <v>2016</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
@@ -12132,7 +12132,7 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5709.5</v>
+        <v>5740.5</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
@@ -12193,17 +12193,17 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>JUBLINGREA</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>Jubilant Ingrevia Ltd.</t>
         </is>
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D148" t="inlineStr">
@@ -12212,26 +12212,26 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>514.35</v>
+        <v>720.4</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>498.25 - 501.9 DR DEMAND</t>
+          <t>538.29 - 548.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>507.3 - 535.36 RD SUPPLY</t>
+          <t>711.35 - 766.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="I148" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J148" t="inlineStr">
@@ -12241,7 +12241,7 @@
       </c>
       <c r="K148" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L148" t="inlineStr">
@@ -12256,7 +12256,7 @@
       </c>
       <c r="N148" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O148" t="inlineStr">
@@ -12273,17 +12273,17 @@
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PPLPHARMA</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
         <is>
-          <t>Piramal Pharma Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D149" t="inlineStr">
@@ -12292,26 +12292,26 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>209.64</v>
+        <v>431</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>208.0 - 215.85 RD SUPPLY</t>
+          <t>430.02 - 431.11 RD SUPPLY</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>132.3 - 136.54 DR DEMAND</t>
+          <t>429.62 - 438.85 RD SUPPLY</t>
         </is>
       </c>
       <c r="I149" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J149" t="inlineStr">
@@ -12336,7 +12336,7 @@
       </c>
       <c r="N149" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O149" t="inlineStr">
@@ -12353,17 +12353,17 @@
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D150" t="inlineStr">
@@ -12372,26 +12372,26 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>721.3</v>
+        <v>519</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>625.59 - 627.84 DR DEMAND</t>
+          <t>498.25 - 501.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>507.3 - 535.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I150" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J150" t="inlineStr">
@@ -12416,7 +12416,7 @@
       </c>
       <c r="N150" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O150" t="inlineStr">
@@ -12433,12 +12433,12 @@
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>KAJARIACER</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Kajaria Ceramics Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
@@ -12452,21 +12452,21 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>1208.9</v>
+        <v>711.2</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>1060.5 - 1072.6 DR DEMAND</t>
+          <t>625.59 - 627.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>1187.65 - 1246.8 RD SUPPLY</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I151" t="inlineStr">
@@ -12513,17 +12513,17 @@
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
@@ -12532,26 +12532,26 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>1184.4</v>
+        <v>1220.7</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>1135.3 - 1139.4 DR DEMAND</t>
+          <t>1060.5 - 1072.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>1187.65 - 1246.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I152" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J152" t="inlineStr">
@@ -12576,7 +12576,7 @@
       </c>
       <c r="N152" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O152" t="inlineStr">
@@ -12593,17 +12593,17 @@
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>PCBL</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>Info Edge (India) Ltd.</t>
+          <t>PCBL Chemical Ltd.</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D153" t="inlineStr">
@@ -12612,26 +12612,26 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>1378.4</v>
+        <v>319.85</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>1358.81 - 1381.39 RD SUPPLY</t>
+          <t>308.15 - 309.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>1474.21 - 1535.33 RD SUPPLY</t>
+          <t>305.14 - 326.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="I153" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J153" t="inlineStr">
@@ -12641,7 +12641,7 @@
       </c>
       <c r="K153" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L153" t="inlineStr">
@@ -12656,7 +12656,7 @@
       </c>
       <c r="N153" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O153" t="inlineStr">
@@ -12673,12 +12673,12 @@
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>Motilal Oswal Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
@@ -12692,26 +12692,26 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>185.68</v>
+        <v>973.4</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>183.76 - 189.37 RD SUPPLY</t>
+          <t>829.0 - 831.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>952.5 - 989.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="I154" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J154" t="inlineStr">
@@ -12721,7 +12721,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L154" t="inlineStr">
@@ -12736,7 +12736,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O154" t="inlineStr">
@@ -12753,78 +12753,638 @@
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
+          <t>PVRINOX</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>PVR INOX Ltd.</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E155" t="n">
+        <v>1219.5</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>1130.0 - 1135.0 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>5.0 C</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="J155" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K155" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L155" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>4.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O155" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P155" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>HOMEFIRST</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Home First Finance Company India Ltd.</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E156" t="n">
+        <v>1187.4</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>1135.3 - 1139.4 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr">
+        <is>
+          <t>1184.37 - 1233.14 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="J156" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K156" t="inlineStr">
+        <is>
+          <t>🟡 1 TEST (TESTED)</t>
+        </is>
+      </c>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>4.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P156" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>AU Small Finance Bank Ltd.</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>BANK</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E157" t="n">
+        <v>1088</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>1087.6 - 1105.9 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>3.5 C</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr">
+        <is>
+          <t>830.84 - 841.88 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I157" t="inlineStr">
+        <is>
+          <t>8.0 A</t>
+        </is>
+      </c>
+      <c r="J157" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K157" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L157" t="inlineStr">
+        <is>
+          <t>🔥 1.8x HIGH VOL</t>
+        </is>
+      </c>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>3.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O157" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P157" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Info Edge (India) Ltd.</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E158" t="n">
+        <v>1360.9</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>1358.81 - 1381.39 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>3.5 C</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>1474.21 - 1535.33 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="J158" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>3.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O158" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P158" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>HYUNDAI</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Hyundai Motor India Ltd.</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>AUTO</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E159" t="n">
+        <v>2227</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>2223.0 - 2251.5 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G159" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H159" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J159" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K159" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L159" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N159" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O159" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P159" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>Life Insurance Corporation of India</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E160" t="n">
+        <v>419</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>452.84 - 457.74 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G160" t="inlineStr">
+        <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr">
+        <is>
+          <t>414.97 - 443.6 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="J160" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K160" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L160" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O160" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P160" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
           <t>POONAWALLA</t>
         </is>
       </c>
-      <c r="B155" t="inlineStr">
+      <c r="B161" t="inlineStr">
         <is>
           <t>Poonawalla Fincorp Ltd.</t>
         </is>
       </c>
-      <c r="C155" t="inlineStr">
+      <c r="C161" t="inlineStr">
         <is>
           <t>FINSERVICE</t>
         </is>
       </c>
-      <c r="D155" t="inlineStr">
+      <c r="D161" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="E155" t="n">
-        <v>493.3</v>
-      </c>
-      <c r="F155" t="inlineStr">
+      <c r="E161" t="n">
+        <v>494.05</v>
+      </c>
+      <c r="F161" t="inlineStr">
         <is>
           <t>425.0 - 428.45 DR DEMAND</t>
         </is>
       </c>
-      <c r="G155" t="inlineStr">
+      <c r="G161" t="inlineStr">
         <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H155" t="inlineStr">
+      <c r="H161" t="inlineStr">
         <is>
           <t>454.8 - 503.0 RD SUPPLY</t>
         </is>
       </c>
-      <c r="I155" t="inlineStr">
+      <c r="I161" t="inlineStr">
         <is>
           <t>3.0 C</t>
         </is>
       </c>
-      <c r="J155" t="inlineStr">
+      <c r="J161" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K155" t="inlineStr">
+      <c r="K161" t="inlineStr">
         <is>
           <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
-      <c r="L155" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M155" t="inlineStr">
+      <c r="L161" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M161" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N155" t="inlineStr">
+      <c r="N161" t="inlineStr">
         <is>
           <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O155" t="inlineStr">
+      <c r="O161" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P155" t="inlineStr">
+      <c r="P161" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>360ONE</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>360 ONE WAM Ltd.</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E162" t="n">
+        <v>1203</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>1047.7 - 1054.9 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G162" t="inlineStr">
+        <is>
+          <t>4.5 C</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>1185.06 - 1260.04 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="J162" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K162" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L162" t="inlineStr">
+        <is>
+          <t>🔥 1.8x HIGH VOL</t>
+        </is>
+      </c>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O162" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P162" t="inlineStr">
         <is>
           <t>IN</t>
         </is>

--- a/NIFTY500_GTF_Dashboard.xlsx
+++ b/NIFTY500_GTF_Dashboard.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P143"/>
+  <dimension ref="A1:P148"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,17 +513,17 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>DEVYANI</t>
+          <t>FIVESTAR</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Devyani International Ltd.</t>
+          <t>Five-Star Business Finance Ltd.</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -532,21 +532,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>138.05</v>
+        <v>523.05</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>137.35 - 138.5 DR DEMAND</t>
+          <t>518.5 - 524.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>91.55 - 94.59 DR DEMAND</t>
+          <t>412.05 - 443.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -566,17 +566,17 @@
       </c>
       <c r="L2" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>9.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O2" t="inlineStr">
@@ -593,17 +593,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ARE&amp;M</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
+          <t>SRF Ltd.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -612,26 +612,26 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>860.4</v>
+        <v>2547</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>859.05 - 861.85 DR DEMAND</t>
+          <t>2490.27 - 2518.02 DR DEMAND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>9.5 A+</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>3066.4 - 3131.26 RD SUPPLY</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -656,34 +656,34 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>9.0 / 10 SOLID</t>
+          <t>11.5 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>BUY READY</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>RKFORGE</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Ramkrishna Forgings Ltd.</t>
+          <t>Apollo Hospitals Enterprise Ltd.</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -692,26 +692,26 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>726.85</v>
+        <v>8650</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>713.35 - 716.65 DR DEMAND</t>
+          <t>8544.05 - 8590.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>459.41 - 465.85 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -731,12 +731,12 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>11.5 / 10 SUPER COMBO</t>
+          <t>11.0 / 10 SUPER COMBO</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -753,17 +753,17 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Apollo Hospitals Enterprise Ltd.</t>
+          <t>Bharat Dynamics Ltd.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -772,11 +772,11 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>8692</v>
+        <v>1255</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>8544.05 - 8590.0 DR DEMAND</t>
+          <t>1232.5 - 1240.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -786,17 +786,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1155.2 - 1204.6 DR DEMAND</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N5" t="inlineStr">
@@ -833,17 +833,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Bharat Dynamics Ltd.</t>
+          <t>Yes Bank Ltd.</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -852,11 +852,11 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1257.7</v>
+        <v>22.5</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>1232.5 - 1240.0 DR DEMAND</t>
+          <t>21.98 - 22.07 DR DEMAND</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -866,12 +866,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1155.2 - 1204.6 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -913,17 +913,17 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>GPIL</t>
+          <t>COROMANDEL</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Godawari Power &amp; Ispat Ltd.</t>
+          <t>Coromandel International Ltd.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
@@ -932,26 +932,26 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>239.9</v>
+        <v>1938.8</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>232.9 - 235.43 DR DEMAND</t>
+          <t>1898.45 - 1912.04 DR DEMAND</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>220.3 - 234.23 DR DEMAND</t>
+          <t>1704.84 - 1751.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>11.0 / 10 SUPER COMBO</t>
+          <t>10.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -993,17 +993,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Aditya Birla Capital Ltd.</t>
+          <t>Dalmia Bharat Ltd.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1012,31 +1012,31 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>402</v>
+        <v>1749.3</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>393.9 - 396.0 DR DEMAND</t>
+          <t>1683.0 - 1730.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>287.7 - 292.25 DR DEMAND</t>
+          <t>2397.36 - 2484.34 RD SUPPLY</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1073,17 +1073,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>COROMANDEL</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Coromandel International Ltd.</t>
+          <t>Titan Company Ltd.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1092,11 +1092,11 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1931.3</v>
+        <v>5020</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>1898.45 - 1912.04 DR DEMAND</t>
+          <t>4886.2 - 4932.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -1106,7 +1106,7 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1704.84 - 1751.89 DR DEMAND</t>
+          <t>3949.84 - 4061.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
@@ -1116,7 +1116,7 @@
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1131,7 +1131,7 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N9" t="inlineStr">
@@ -1153,17 +1153,17 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Titan Company Ltd.</t>
+          <t>Colgate Palmolive (India) Ltd.</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1172,31 +1172,31 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>5027</v>
+        <v>1829.2</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>4886.2 - 4932.0 DR DEMAND</t>
+          <t>1803.7 - 1826.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
+          <t>8.0 A</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>2228.23 - 2274.78 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
           <t>8.5 A</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>3949.84 - 4061.57 DR DEMAND</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>10.5 / 10 HIGH COMBO</t>
+          <t>10.0 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -1233,17 +1233,17 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>INDIGO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Colgate Palmolive (India) Ltd.</t>
+          <t>InterGlobe Aviation Ltd.</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1252,26 +1252,26 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1850</v>
+        <v>4977</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>1803.7 - 1826.0 DR DEMAND</t>
+          <t>4945.9 - 4961.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2228.23 - 2274.78 RD SUPPLY</t>
+          <t>5901.5 - 5970.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N11" t="inlineStr">
@@ -1313,17 +1313,17 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FIVESTAR</t>
+          <t>SONACOMS</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Five-Star Business Finance Ltd.</t>
+          <t>Sona BLW Precision Forgings Ltd.</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1332,11 +1332,11 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>534.6</v>
+        <v>789</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>518.5 - 524.85 DR DEMAND</t>
+          <t>773.4 - 782.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -1346,7 +1346,7 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>412.05 - 443.54 DR DEMAND</t>
+          <t>399.83 - 409.23 DR DEMAND</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
@@ -1393,12 +1393,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>INDIGO</t>
+          <t>BLUEDART</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>InterGlobe Aviation Ltd.</t>
+          <t>Blue Dart Express Ltd.</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -1412,26 +1412,26 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>4980</v>
+        <v>4991.7</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>4945.9 - 4961.4 DR DEMAND</t>
+          <t>4902.5 - 4920.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>5901.5 - 5970.0 RD SUPPLY</t>
+          <t>5465.7 - 5775.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1456,7 +1456,7 @@
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>10.0 / 10 HIGH COMBO</t>
+          <t>9.5 / 10 HIGH COMBO</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
@@ -1473,17 +1473,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>EIDPARRY</t>
+          <t>ICICIBANK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>E.I.D. Parry (India) Ltd.</t>
+          <t>ICICI Bank Ltd.</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -1492,31 +1492,31 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>778.25</v>
+        <v>1423.2</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>759.0 - 763.0 DR DEMAND</t>
+          <t>1401.0 - 1403.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>639.0 - 660.0 DR DEMAND</t>
+          <t>1457.77 - 1476.07 RD SUPPLY</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1553,17 +1553,17 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>SBILIFE</t>
+          <t>NEULANDLAB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>SBI Life Insurance Company Ltd.</t>
+          <t>Neuland Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -1572,31 +1572,31 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>1715</v>
+        <v>22660</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>1700.4 - 1706.0 DR DEMAND</t>
+          <t>22123.0 - 22216.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>1700.4 - 1765.7 DR DEMAND</t>
+          <t>10163.48 - 10582.66 DR DEMAND</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="M15" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N15" t="inlineStr">
@@ -1633,17 +1633,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>VIJAYA</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Vijaya Diagnostic Centre Ltd.</t>
+          <t>Supreme Industries Ltd.</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1652,11 +1652,11 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1505.5</v>
+        <v>3475</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>1475.0 - 1478.3 DR DEMAND</t>
+          <t>3403.1 - 3422.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -1666,17 +1666,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>848.0 - 861.4 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -1691,7 +1691,7 @@
       </c>
       <c r="M16" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N16" t="inlineStr">
@@ -1713,17 +1713,17 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWL</t>
+          <t>ARE&amp;M</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>AWL Agri Business Ltd.</t>
+          <t>Amara Raja Energy &amp; Mobility Ltd.</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
@@ -1732,11 +1732,11 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>190.79</v>
+        <v>864.2</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>187.33 - 188.12 DR DEMAND</t>
+          <t>859.05 - 861.85 DR DEMAND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -1793,17 +1793,17 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>LTM</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>LTM Ltd.</t>
+          <t>Bajaj Finance Ltd.</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -1812,28 +1812,28 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>4560</v>
+        <v>1060.5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>4512.9 - 4540.0 DR DEMAND</t>
+          <t>1043.2 - 1049.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>783.09 - 796.65 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
           <t>7.0 A</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J18" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -1851,7 +1851,7 @@
       </c>
       <c r="M18" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N18" t="inlineStr">
@@ -1873,17 +1873,17 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>NEULANDLAB</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Neuland Laboratories Ltd.</t>
+          <t>Indian Hotels Co. Ltd.</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1892,11 +1892,11 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>22890</v>
+        <v>720</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>22419.0 - 22510.0 DR DEMAND</t>
+          <t>706.05 - 713.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>10163.49 - 10582.66 DR DEMAND</t>
+          <t>871.1 - 888.32 RD SUPPLY</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1953,17 +1953,17 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>OLECTRA</t>
+          <t>LTM</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Olectra Greentech Ltd.</t>
+          <t>LTM Ltd.</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -1972,11 +1972,11 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1244.8</v>
+        <v>4554</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>1219.4 - 1225.3 DR DEMAND</t>
+          <t>4512.9 - 4540.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -1986,17 +1986,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>1508.5 - 1556.0 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2011,7 +2011,7 @@
       </c>
       <c r="M20" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N20" t="inlineStr">
@@ -2033,17 +2033,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Pidilite Industries Ltd.</t>
+          <t>MphasiS Ltd.</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -2052,16 +2052,16 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1638.3</v>
+        <v>2422</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>1601.0 - 1611.4 DR DEMAND</t>
+          <t>2375.4 - 2380.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2081,7 +2081,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L21" t="inlineStr">
@@ -2091,7 +2091,7 @@
       </c>
       <c r="M21" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N21" t="inlineStr">
@@ -2113,17 +2113,17 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>SAGILITY</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Sagility Ltd.</t>
+          <t>Pidilite Industries Ltd.</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -2132,26 +2132,26 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>46.8</v>
+        <v>1629.5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>45.82 - 46.0 DR DEMAND</t>
+          <t>1601.0 - 1611.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1687.7 - 1707.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
@@ -2161,7 +2161,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L22" t="inlineStr">
@@ -2171,7 +2171,7 @@
       </c>
       <c r="M22" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N22" t="inlineStr">
@@ -2193,17 +2193,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Tata Consumer Products Ltd.</t>
+          <t>PB Fintech Ltd.</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
@@ -2212,21 +2212,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1019.2</v>
+        <v>1836</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>1090.5 - 1095.0 RD SUPPLY</t>
+          <t>1796.4 - 1811.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>998.75 - 1006.29 DR DEMAND</t>
+          <t>2108.85 - 2246.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
@@ -2236,12 +2236,12 @@
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L23" t="inlineStr">
@@ -2273,17 +2273,17 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>RKFORGE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>UltraTech Cement Ltd.</t>
+          <t>Ramkrishna Forgings Ltd.</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
@@ -2292,21 +2292,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>11275</v>
+        <v>700.85</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>11062.2 - 11125.9 DR DEMAND</t>
+          <t>688.35 - 693.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>9784.84 - 9863.33 DR DEMAND</t>
+          <t>459.41 - 465.85 DR DEMAND</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2316,12 +2316,12 @@
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L24" t="inlineStr">
@@ -2353,17 +2353,17 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ABBOTINDIA</t>
+          <t>SAGILITY</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Abbott India Ltd.</t>
+          <t>Sagility Ltd.</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
@@ -2372,31 +2372,31 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>25945</v>
+        <v>46.82</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>25527.65 - 25600.93 DR DEMAND</t>
+          <t>45.82 - 46.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>24406.02 - 25223.54 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -2416,7 +2416,7 @@
       </c>
       <c r="N25" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O25" t="inlineStr">
@@ -2433,17 +2433,17 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ACC</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>ACC Ltd.</t>
+          <t>Tata Consumer Products Ltd.</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
@@ -2452,26 +2452,26 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1272</v>
+        <v>1010</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>1244.5 - 1247.38 DR DEMAND</t>
+          <t>1090.5 - 1095.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>998.75 - 1006.29 DR DEMAND</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="N26" t="inlineStr">
         <is>
-          <t>8.5 / 10 SOLID</t>
+          <t>9.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O26" t="inlineStr">
@@ -2513,17 +2513,17 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>DATAPATTNS</t>
+          <t>ABBOTINDIA</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Data Patterns (India) Ltd.</t>
+          <t>Abbott India Ltd.</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
@@ -2532,36 +2532,36 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4587.3</v>
+        <v>26065</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>4500.1 - 4542.3 DR DEMAND</t>
+          <t>25527.65 - 25600.93 DR DEMAND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>1344.18 - 1430.33 DR DEMAND</t>
+          <t>24406.02 - 25223.54 DR DEMAND</t>
         </is>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L27" t="inlineStr">
@@ -2571,7 +2571,7 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N27" t="inlineStr">
@@ -2593,17 +2593,17 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>LATENTVIEW</t>
+          <t>DATAPATTNS</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Latent View Analytics Ltd.</t>
+          <t>Data Patterns (India) Ltd.</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -2612,36 +2612,36 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>266</v>
+        <v>4585</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>262.05 - 264.25 DR DEMAND</t>
+          <t>4500.1 - 4542.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>262.05 - 270.8 DR DEMAND</t>
+          <t>1344.18 - 1430.33 DR DEMAND</t>
         </is>
       </c>
       <c r="I28" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J28" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L28" t="inlineStr">
@@ -2651,7 +2651,7 @@
       </c>
       <c r="M28" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N28" t="inlineStr">
@@ -2673,17 +2673,17 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MGL</t>
+          <t>GMDCLTD</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Mahanagar Gas Ltd.</t>
+          <t>Gujarat Mineral Development Corporation Ltd.</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
@@ -2692,11 +2692,11 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1066.4</v>
+        <v>562.95</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>1054.52 - 1061.5 DR DEMAND</t>
+          <t>552.0 - 553.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -2706,12 +2706,12 @@
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>885.65 - 912.91 DR DEMAND</t>
+          <t>736.15 - 771.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J29" t="inlineStr">
@@ -2753,17 +2753,17 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>CASTROLIND</t>
+          <t>HDBFS</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Castrol India Ltd.</t>
+          <t>HDB Financial Services Ltd.</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
@@ -2772,31 +2772,31 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>186.42</v>
+        <v>682.7</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>184.1 - 184.49 DR DEMAND</t>
+          <t>671.9 - 675.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>144.37 - 156.26 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
@@ -2816,7 +2816,7 @@
       </c>
       <c r="N30" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O30" t="inlineStr">
@@ -2833,17 +2833,17 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>GODFRYPHLP</t>
+          <t>LATENTVIEW</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Godfrey Phillips India Ltd.</t>
+          <t>Latent View Analytics Ltd.</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D31" t="inlineStr">
@@ -2852,11 +2852,11 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>2045</v>
+        <v>267.25</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>1998.17 - 2008.62 DR DEMAND</t>
+          <t>262.05 - 264.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
@@ -2866,12 +2866,12 @@
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>262.05 - 270.8 DR DEMAND</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L31" t="inlineStr">
@@ -2891,12 +2891,12 @@
       </c>
       <c r="M31" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N31" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O31" t="inlineStr">
@@ -2913,17 +2913,17 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>NAVA</t>
+          <t>MINDACORP</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Nava Ltd.</t>
+          <t>Minda Corporation Ltd.</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D32" t="inlineStr">
@@ -2932,31 +2932,31 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>557.2</v>
+        <v>702.8</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>545.15 - 549.2 DR DEMAND</t>
+          <t>685.5 - 690.65 DR DEMAND</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>497.01 - 517.17 DR DEMAND</t>
+          <t>451.85 - 473.12 DR DEMAND</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="N32" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O32" t="inlineStr">
@@ -2993,17 +2993,17 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>SYNGENE</t>
+          <t>NATCOPHARM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Syngene International Ltd.</t>
+          <t>NATCO Pharma Ltd.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
@@ -3012,21 +3012,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>400.8</v>
+        <v>828.65</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>394.9 - 395.5 DR DEMAND</t>
+          <t>950.09 - 963.22 RD SUPPLY</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>711.99 - 726.54 RD SUPPLY</t>
+          <t>803.32 - 821.11 DR DEMAND</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
@@ -3056,7 +3056,7 @@
       </c>
       <c r="N33" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>8.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O33" t="inlineStr">
@@ -3073,17 +3073,17 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>ASIANPAINT</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Tata Motors Passenger Vehicles Ltd.</t>
+          <t>Asian Paints Ltd.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
@@ -3092,26 +3092,26 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>312</v>
+        <v>2527.3</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>305.65 - 307.7 DR DEMAND</t>
+          <t>2478.5 - 2483.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>391.75 - 404.64 RD SUPPLY</t>
+          <t>2083.96 - 2137.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J34" t="inlineStr">
@@ -3131,7 +3131,7 @@
       </c>
       <c r="M34" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N34" t="inlineStr">
@@ -3153,17 +3153,17 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>BSOFT</t>
+          <t>MUTHOOTFIN</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Birlasoft Ltd.</t>
+          <t>Muthoot Finance Ltd.</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
@@ -3172,28 +3172,28 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>293.25</v>
+        <v>2913.8</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>287.25 - 287.95 DR DEMAND</t>
+          <t>2840.0 - 2870.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>2064.17 - 2088.91 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr">
-        <is>
-          <t>421.73 - 438.51 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>7.0 A</t>
-        </is>
-      </c>
       <c r="J35" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3211,12 +3211,12 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N35" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O35" t="inlineStr">
@@ -3233,17 +3233,17 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>GODREJPROP</t>
+          <t>NHPC</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Godrej Properties Ltd.</t>
+          <t>NHPC Ltd.</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
@@ -3252,21 +3252,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>2001.5</v>
+        <v>76.25</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>1962.91 - 1969.98 DR DEMAND</t>
+          <t>74.3 - 74.82 DR DEMAND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>1427.1 - 1464.22 DR DEMAND</t>
+          <t>67.83 - 70.98 DR DEMAND</t>
         </is>
       </c>
       <c r="I36" t="inlineStr">
@@ -3276,17 +3276,17 @@
       </c>
       <c r="J36" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L36" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M36" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="N36" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O36" t="inlineStr">
@@ -3313,17 +3313,17 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>HONAUT</t>
+          <t>RECLTD</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Honeywell Automation India Ltd.</t>
+          <t>REC Ltd.</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -3332,16 +3332,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>35265</v>
+        <v>318.7</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>34926.25 - 35130.67 DR DEMAND</t>
+          <t>312.2 - 313.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -3361,7 +3361,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L37" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="N37" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O37" t="inlineStr">
@@ -3393,17 +3393,17 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>IGL</t>
+          <t>SYNGENE</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Indraprastha Gas Ltd.</t>
+          <t>Syngene International Ltd.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D38" t="inlineStr">
@@ -3412,26 +3412,26 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>149.42</v>
+        <v>395.6</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>147.45 - 147.94 DR DEMAND</t>
+          <t>394.9 - 395.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>141.74 - 145.62 DR DEMAND</t>
+          <t>711.99 - 726.54 RD SUPPLY</t>
         </is>
       </c>
       <c r="I38" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J38" t="inlineStr">
@@ -3451,12 +3451,12 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N38" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O38" t="inlineStr">
@@ -3473,17 +3473,17 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>LEMONTREE</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Lemon Tree Hotels Ltd.</t>
+          <t>Tata Motors Passenger Vehicles Ltd.</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D39" t="inlineStr">
@@ -3492,28 +3492,28 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>104.89</v>
+        <v>311.5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>103.5 - 103.68 DR DEMAND</t>
+          <t>305.65 - 307.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>391.75 - 404.64 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
           <t>6.5 B</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J39" t="inlineStr">
         <is>
           <t>1W DOWN • 20 EMA BEARISH</t>
@@ -3531,12 +3531,12 @@
       </c>
       <c r="M39" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N39" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O39" t="inlineStr">
@@ -3553,17 +3553,17 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>MANKIND</t>
+          <t>BSOFT</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Mankind Pharma Ltd.</t>
+          <t>Birlasoft Ltd.</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
@@ -3572,11 +3572,11 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>2368.8</v>
+        <v>289.35</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2341.2 - 2351.0 DR DEMAND</t>
+          <t>287.25 - 287.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
@@ -3586,12 +3586,12 @@
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>1909.7 - 2005.8 DR DEMAND</t>
+          <t>421.73 - 438.51 RD SUPPLY</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J40" t="inlineStr">
@@ -3633,12 +3633,12 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>TRIDENT</t>
+          <t>DEVYANI</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Trident Ltd.</t>
+          <t>Devyani International Ltd.</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -3652,36 +3652,36 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>23.99</v>
+        <v>139.28</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>23.51 - 23.57 DR DEMAND</t>
+          <t>137.35 - 138.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>91.55 - 94.59 DR DEMAND</t>
         </is>
       </c>
       <c r="I41" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J41" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L41" t="inlineStr">
@@ -3713,17 +3713,17 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>SHRIRAMFIN</t>
+          <t>GODREJPROP</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Shriram Finance Ltd.</t>
+          <t>Godrej Properties Ltd.</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -3732,26 +3732,26 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>1044.2</v>
+        <v>1982</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>1019.5 - 1027.2 DR DEMAND</t>
+          <t>1962.91 - 1969.98 DR DEMAND</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>559.9 - 573.24 DR DEMAND</t>
+          <t>1427.1 - 1464.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="N42" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O42" t="inlineStr">
@@ -3793,17 +3793,17 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>BLUEJET</t>
+          <t>HONAUT</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Blue Jet Healthcare Ltd.</t>
+          <t>Honeywell Automation India Ltd.</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D43" t="inlineStr">
@@ -3812,31 +3812,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>579</v>
+        <v>35655</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>570.5 - 571.95 DR DEMAND</t>
+          <t>34926.25 - 35130.67 DR DEMAND</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>633.0 - 647.8 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K43" t="inlineStr">
@@ -3851,12 +3851,12 @@
       </c>
       <c r="M43" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N43" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O43" t="inlineStr">
@@ -3873,17 +3873,17 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>ENRIN</t>
+          <t>LEMONTREE</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Siemens Energy India Ltd.</t>
+          <t>Lemon Tree Hotels Ltd.</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -3892,16 +3892,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>3155.2</v>
+        <v>104.95</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>3075.0 - 3121.7 DR DEMAND</t>
+          <t>103.5 - 103.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -3921,7 +3921,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L44" t="inlineStr">
@@ -3931,12 +3931,12 @@
       </c>
       <c r="M44" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N44" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O44" t="inlineStr">
@@ -3953,17 +3953,17 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ERIS</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Indian Energy Exchange Ltd.</t>
+          <t>Eris Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -3972,16 +3972,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>119.15</v>
+        <v>1321.7</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>116.8 - 117.07 DR DEMAND</t>
+          <t>1288.9 - 1301.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -4001,7 +4001,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L45" t="inlineStr">
@@ -4011,12 +4011,12 @@
       </c>
       <c r="M45" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N45" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O45" t="inlineStr">
@@ -4033,12 +4033,12 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>MSUMI</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Motherson Sumi Wiring India Ltd.</t>
+          <t>Exide Industries Ltd.</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -4052,31 +4052,31 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>37.03</v>
+        <v>424.35</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>35.19 - 35.38 DR DEMAND</t>
+          <t>420.35 - 423.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>36.14 - 36.57 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I46" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J46" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="N46" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O46" t="inlineStr">
@@ -4113,17 +4113,17 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>UBL</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>United Breweries Ltd.</t>
+          <t>Mahindra &amp; Mahindra Ltd.</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D47" t="inlineStr">
@@ -4132,26 +4132,26 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1284.2</v>
+        <v>3170</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>1266.98 - 1276.91 DR DEMAND</t>
+          <t>3135.1 - 3161.4 DR DEMAND</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>1426.85 - 1453.66 RD SUPPLY</t>
+          <t>3465.0 - 3534.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I47" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J47" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M47" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="N47" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O47" t="inlineStr">
@@ -4193,17 +4193,17 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>BAJAJHFL</t>
+          <t>POWERINDIA</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Bajaj Housing Finance Ltd.</t>
+          <t>Hitachi Energy India Ltd.</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -4212,26 +4212,26 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>82.95</v>
+        <v>31650</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>82.4 - 82.53 DR DEMAND</t>
+          <t>30392.74 - 31032.59 DR DEMAND</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>10919.68 - 11972.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I48" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J48" t="inlineStr">
@@ -4256,7 +4256,7 @@
       </c>
       <c r="N48" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O48" t="inlineStr">
@@ -4273,17 +4273,17 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>SHRIRAMFIN</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Bharat Electronics Ltd.</t>
+          <t>Shriram Finance Ltd.</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D49" t="inlineStr">
@@ -4292,11 +4292,11 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>408.6</v>
+        <v>1041</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>405.55 - 407.0 DR DEMAND</t>
+          <t>1019.5 - 1027.2 DR DEMAND</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -4306,22 +4306,22 @@
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>378.32 - 397.37 DR DEMAND</t>
+          <t>559.9 - 573.24 DR DEMAND</t>
         </is>
       </c>
       <c r="I49" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J49" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L49" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="N49" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O49" t="inlineStr">
@@ -4353,17 +4353,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CENTRALBK</t>
+          <t>HINDZINC</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Central Bank of India</t>
+          <t>Hindustan Zinc Ltd.</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
@@ -4372,36 +4372,36 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>30.77</v>
+        <v>601</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>30.1 - 30.17 DR DEMAND</t>
+          <t>586.85 - 592.6 DR DEMAND</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>35.83 - 36.93 RD SUPPLY</t>
+          <t>475.32 - 493.14 DR DEMAND</t>
         </is>
       </c>
       <c r="I50" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J50" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L50" t="inlineStr">
@@ -4416,7 +4416,7 @@
       </c>
       <c r="N50" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O50" t="inlineStr">
@@ -4433,17 +4433,17 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CUMMINSIND</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cummins India Ltd.</t>
+          <t>Indian Energy Exchange Ltd.</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
@@ -4452,26 +4452,26 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5071</v>
+        <v>118.91</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>5037.62 - 5058.05 DR DEMAND</t>
+          <t>116.8 - 117.07 DR DEMAND</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>4357.85 - 4463.08 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I51" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J51" t="inlineStr">
@@ -4486,7 +4486,7 @@
       </c>
       <c r="L51" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M51" t="inlineStr">
@@ -4496,7 +4496,7 @@
       </c>
       <c r="N51" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O51" t="inlineStr">
@@ -4513,17 +4513,17 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>LTTS</t>
+          <t>PFIZER</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>L&amp;T Technology Services Ltd.</t>
+          <t>Pfizer Ltd.</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
@@ -4532,31 +4532,31 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3501.2</v>
+        <v>4609.7</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>3460.0 - 3476.8 DR DEMAND</t>
+          <t>4502.6 - 4545.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>2976.44 - 3086.89 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I52" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J52" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K52" t="inlineStr">
@@ -4576,7 +4576,7 @@
       </c>
       <c r="N52" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O52" t="inlineStr">
@@ -4593,17 +4593,17 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Power Finance Corporation Ltd.</t>
+          <t>PG Electroplast Ltd.</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
@@ -4612,26 +4612,26 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>345.5</v>
+        <v>562.3</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>431.25 - 433.95 RD SUPPLY</t>
+          <t>551.85 - 553.9 DR DEMAND</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>329.74 - 339.39 DR DEMAND</t>
+          <t>811.74 - 836.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I53" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J53" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="K53" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L53" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="M53" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N53" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O53" t="inlineStr">
@@ -4673,12 +4673,12 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>RAMCOCEM</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>The Ramco Cements Ltd.</t>
+          <t>Premier Energies Ltd.</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -4692,26 +4692,26 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>879.15</v>
+        <v>1002</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>856.75 - 860.55 DR DEMAND</t>
+          <t>977.4 - 982.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>836.02 - 868.83 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I54" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J54" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="N54" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O54" t="inlineStr">
@@ -4753,17 +4753,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>ABDL</t>
+          <t>SBILIFE</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Allied Blenders and Distillers Ltd.</t>
+          <t>SBI Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D55" t="inlineStr">
@@ -4772,41 +4772,41 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>609.4</v>
+        <v>1775</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>584.75 - 598.5 DR DEMAND</t>
+          <t>1700.4 - 1706.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>378.82 - 400.58 DR DEMAND</t>
+          <t>1700.4 - 1765.7 DR DEMAND</t>
         </is>
       </c>
       <c r="I55" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J55" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K55" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M55" t="inlineStr">
@@ -4816,7 +4816,7 @@
       </c>
       <c r="N55" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O55" t="inlineStr">
@@ -4833,17 +4833,17 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ALKEM</t>
+          <t>UBL</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Alkem Laboratories Ltd.</t>
+          <t>United Breweries Ltd.</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D56" t="inlineStr">
@@ -4852,26 +4852,26 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5193</v>
+        <v>1279.4</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>5102.37 - 5135.31 DR DEMAND</t>
+          <t>1266.98 - 1276.91 DR DEMAND</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1426.85 - 1453.66 RD SUPPLY</t>
         </is>
       </c>
       <c r="I56" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J56" t="inlineStr">
@@ -4886,17 +4886,17 @@
       </c>
       <c r="L56" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M56" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N56" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O56" t="inlineStr">
@@ -4913,12 +4913,12 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>CAMS</t>
+          <t>BAJAJHFL</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Computer Age Management Services Ltd.</t>
+          <t>Bajaj Housing Finance Ltd.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -4932,26 +4932,26 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>747.4</v>
+        <v>83.08</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>737.82 - 743.27 DR DEMAND</t>
+          <t>82.4 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>591.51 - 613.37 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I57" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J57" t="inlineStr">
@@ -4961,7 +4961,7 @@
       </c>
       <c r="K57" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L57" t="inlineStr">
@@ -4976,7 +4976,7 @@
       </c>
       <c r="N57" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O57" t="inlineStr">
@@ -4993,17 +4993,17 @@
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>MAXHEALTH</t>
+          <t>LTTS</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Max Healthcare Institute Ltd.</t>
+          <t>L&amp;T Technology Services Ltd.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
@@ -5012,11 +5012,11 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>994.9</v>
+        <v>3493.3</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>980.3 - 990.5 DR DEMAND</t>
+          <t>3460.0 - 3476.8 DR DEMAND</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
@@ -5026,17 +5026,17 @@
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>937.3 - 958.19 DR DEMAND</t>
+          <t>2976.44 - 3086.89 DR DEMAND</t>
         </is>
       </c>
       <c r="I58" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J58" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K58" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="N58" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O58" t="inlineStr">
@@ -5073,17 +5073,17 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>MEDANTA</t>
+          <t>OLECTRA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Global Health Ltd.</t>
+          <t>Olectra Greentech Ltd.</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D59" t="inlineStr">
@@ -5092,36 +5092,36 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>1417.3</v>
+        <v>1229</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>1382.71 - 1393.91 DR DEMAND</t>
+          <t>1219.4 - 1225.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>1480.9 - 1544.0 RD SUPPLY</t>
+          <t>1508.5 - 1556.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I59" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J59" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K59" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L59" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="M59" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N59" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O59" t="inlineStr">
@@ -5153,17 +5153,17 @@
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>TRITURBINE</t>
+          <t>POLYMED</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Triveni Turbine Ltd.</t>
+          <t>Poly Medicure Ltd.</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
@@ -5172,36 +5172,36 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>571.7</v>
+        <v>1702.5</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>559.11 - 567.68 DR DEMAND</t>
+          <t>1647.83 - 1688.54 DR DEMAND</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1297.34 - 1337.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K60" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L60" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N60" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O60" t="inlineStr">
@@ -5233,17 +5233,17 @@
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>RAMCOCEM</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>State Bank of India</t>
+          <t>The Ramco Cements Ltd.</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D61" t="inlineStr">
@@ -5252,26 +5252,26 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>1023.4</v>
+        <v>884.5</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>1007.4 - 1015.3 DR DEMAND</t>
+          <t>856.75 - 860.55 DR DEMAND</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>933.9 - 964.4 DR DEMAND</t>
+          <t>836.02 - 868.83 DR DEMAND</t>
         </is>
       </c>
       <c r="I61" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J61" t="inlineStr">
@@ -5281,7 +5281,7 @@
       </c>
       <c r="K61" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L61" t="inlineStr">
@@ -5296,7 +5296,7 @@
       </c>
       <c r="N61" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O61" t="inlineStr">
@@ -5313,17 +5313,17 @@
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TECHNOE</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Tata Steel Ltd.</t>
+          <t>Techno Electric &amp; Engineering Company Ltd.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D62" t="inlineStr">
@@ -5332,26 +5332,26 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>184.2</v>
+        <v>979.5</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>182.01 - 182.63 DR DEMAND</t>
+          <t>1030.65 - 1041.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>156.83 - 164.57 DR DEMAND</t>
+          <t>870.0 - 974.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I62" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J62" t="inlineStr">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="K62" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L62" t="inlineStr">
@@ -5376,7 +5376,7 @@
       </c>
       <c r="N62" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O62" t="inlineStr">
@@ -5393,17 +5393,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>BERGEPAINT</t>
+          <t>ABDL</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Berger Paints India Ltd.</t>
+          <t>Allied Blenders and Distillers Ltd.</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D63" t="inlineStr">
@@ -5412,36 +5412,36 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>491.4</v>
+        <v>609.95</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>485.24 - 486.03 DR DEMAND</t>
+          <t>584.75 - 598.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>560.77 - 590.09 RD SUPPLY</t>
+          <t>378.82 - 400.58 DR DEMAND</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K63" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L63" t="inlineStr">
@@ -5451,12 +5451,12 @@
       </c>
       <c r="M63" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N63" t="inlineStr">
         <is>
-          <t>4.0 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O63" t="inlineStr">
@@ -5473,17 +5473,17 @@
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>MMTC</t>
+          <t>CAMS</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>MMTC Ltd.</t>
+          <t>Computer Age Management Services Ltd.</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D64" t="inlineStr">
@@ -5492,26 +5492,26 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>62.32</v>
+        <v>748.8</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>61.55 - 62.15 DR DEMAND</t>
+          <t>737.82 - 743.27 DR DEMAND</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>50.1 - 52.1 DR DEMAND</t>
+          <t>591.51 - 613.37 DR DEMAND</t>
         </is>
       </c>
       <c r="I64" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J64" t="inlineStr">
@@ -5521,7 +5521,7 @@
       </c>
       <c r="K64" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L64" t="inlineStr">
@@ -5531,12 +5531,12 @@
       </c>
       <c r="M64" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N64" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O64" t="inlineStr">
@@ -5553,17 +5553,17 @@
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>VMM</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Vishal Mega Mart Ltd.</t>
+          <t>HDFC Life Insurance Company Ltd.</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D65" t="inlineStr">
@@ -5572,26 +5572,26 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>107.8</v>
+        <v>546.4</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>105.8 - 107.0 DR DEMAND</t>
+          <t>530.5 - 535.95 DR DEMAND</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>811.41 - 817.84 RD SUPPLY</t>
         </is>
       </c>
       <c r="I65" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J65" t="inlineStr">
@@ -5601,22 +5601,22 @@
       </c>
       <c r="K65" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L65" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M65" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N65" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O65" t="inlineStr">
@@ -5633,17 +5633,17 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>DIXON</t>
+          <t>TRITURBINE</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Dixon Technologies (India) Ltd.</t>
+          <t>Triveni Turbine Ltd.</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D66" t="inlineStr">
@@ -5652,36 +5652,36 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>14445</v>
+        <v>577.3</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>14400.0 - 14529.0 DR DEMAND</t>
+          <t>559.11 - 567.68 DR DEMAND</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>16444.68 - 17061.41 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I66" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J66" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K66" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L66" t="inlineStr">
@@ -5691,39 +5691,39 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N66" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>HINDZINC</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Hindustan Zinc Ltd.</t>
+          <t>Zydus Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
@@ -5732,26 +5732,26 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>587.95</v>
+        <v>1120</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>586.85 - 592.6 DR DEMAND</t>
+          <t>1094.12 - 1098.81 DR DEMAND</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>475.32 - 493.14 DR DEMAND</t>
+          <t>855.18 - 875.51 DR DEMAND</t>
         </is>
       </c>
       <c r="I67" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J67" t="inlineStr">
@@ -5761,7 +5761,7 @@
       </c>
       <c r="K67" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L67" t="inlineStr">
@@ -5771,39 +5771,39 @@
       </c>
       <c r="M67" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N67" t="inlineStr">
         <is>
-          <t>8.0 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O67" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>NAM-INDIA</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Nippon Life India Asset Management Ltd.</t>
+          <t>Havells India Ltd.</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
@@ -5812,78 +5812,78 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1164.9</v>
+        <v>1154</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>1161.3 - 1170.6 DR DEMAND</t>
+          <t>1123.6 - 1133.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>483.41 - 495.06 DR DEMAND</t>
+          <t>1390.17 - 1435.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="I68" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J68" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K68" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M68" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N68" t="inlineStr">
         <is>
-          <t>7.5 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O68" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P68" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>RHIM</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Exide Industries Ltd.</t>
+          <t>RHI MAGNESITA INDIA LTD.</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
@@ -5892,36 +5892,36 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>423</v>
+        <v>371.35</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>420.35 - 423.4 DR DEMAND</t>
+          <t>366.95 - 370.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>323.05 - 337.85 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
           <t>4.0 C</t>
         </is>
       </c>
-      <c r="H69" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J69" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K69" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L69" t="inlineStr">
@@ -5936,34 +5936,34 @@
       </c>
       <c r="N69" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O69" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P69" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Mahindra &amp; Mahindra Ltd.</t>
+          <t>State Bank of India</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
@@ -5972,26 +5972,26 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3150</v>
+        <v>1016.1</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>3135.1 - 3161.4 DR DEMAND</t>
+          <t>1007.4 - 1015.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>3465.0 - 3534.6 RD SUPPLY</t>
+          <t>933.9 - 964.4 DR DEMAND</t>
         </is>
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J70" t="inlineStr">
@@ -6001,7 +6001,7 @@
       </c>
       <c r="K70" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L70" t="inlineStr">
@@ -6016,72 +6016,72 @@
       </c>
       <c r="N70" t="inlineStr">
         <is>
-          <t>7.0 / 10 SOLID</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O70" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>ICICIBANK</t>
+          <t>ALKEM</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>ICICI Bank Ltd.</t>
+          <t>Alkem Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>1430</v>
+        <v>5190</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>1401.0 - 1403.0 DR DEMAND</t>
+          <t>5102.37 - 5135.31 DR DEMAND</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>1457.77 - 1476.07 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I71" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J71" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K71" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L71" t="inlineStr">
@@ -6091,67 +6091,67 @@
       </c>
       <c r="M71" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N71" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O71" t="inlineStr">
         <is>
-          <t>WAIT FOR PULLBACK</t>
+          <t>APPROACHING DEMAND</t>
         </is>
       </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>UTIAMC</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>UTI Asset Management Company Ltd.</t>
+          <t>KEI Industries Ltd.</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>EQUILIBRIUM</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>880.4</v>
+        <v>4850</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>897.2 - 904.15 RD SUPPLY</t>
+          <t>5327.0 - 5380.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>841.38 - 874.76 DR DEMAND</t>
+          <t>4745.5 - 4999.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I72" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J72" t="inlineStr">
@@ -6161,22 +6161,22 @@
       </c>
       <c r="K72" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L72" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M72" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N72" t="inlineStr">
         <is>
-          <t>6.5 / 10 SOLID</t>
+          <t>8.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O72" t="inlineStr">
@@ -6186,24 +6186,24 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>CONFLICT</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>IGIL</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>International Gemological Institute Ltd.</t>
+          <t>Fortis Healthcare Ltd.</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D73" t="inlineStr">
@@ -6212,26 +6212,26 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>325.95</v>
+        <v>905</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>323.56 - 326.29 DR DEMAND</t>
+          <t>904.45 - 907.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>765.99 - 794.16 DR DEMAND</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="K73" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L73" t="inlineStr">
@@ -6256,7 +6256,7 @@
       </c>
       <c r="N73" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O73" t="inlineStr">
@@ -6273,17 +6273,17 @@
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>PCBL</t>
+          <t>LICI</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>PCBL Chemical Ltd.</t>
+          <t>Life Insurance Corporation of India</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D74" t="inlineStr">
@@ -6292,26 +6292,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>314.25</v>
+        <v>415.35</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>308.15 - 309.8 DR DEMAND</t>
+          <t>406.8 - 408.25 DR DEMAND</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>305.14 - 326.1 RD SUPPLY</t>
+          <t>414.97 - 443.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="N74" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O74" t="inlineStr">
@@ -6353,45 +6353,45 @@
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>TECHNOE</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Techno Electric &amp; Engineering Company Ltd.</t>
+          <t>Indus Towers Ltd.</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>973.65</v>
+        <v>376.8</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>1030.65 - 1041.5 RD SUPPLY</t>
+          <t>380.5 - 381.3 RD SUPPLY</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>870.0 - 974.5 DR DEMAND</t>
+          <t>376.63 - 395.08 DR DEMAND</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="K75" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L75" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N75" t="inlineStr">
         <is>
-          <t>6.0 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O75" t="inlineStr">
@@ -6426,19 +6426,19 @@
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>BATAINDIA</t>
+          <t>PVRINOX</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Bata India Ltd.</t>
+          <t>PVR INOX Ltd.</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -6452,36 +6452,36 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>677.4</v>
+        <v>1227.2</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>666.85 - 670.45 DR DEMAND</t>
+          <t>1207.0 - 1210.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>685.67 - 743.46 RD SUPPLY</t>
+          <t>1207.7 - 1249.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="I76" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J76" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K76" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L76" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="N76" t="inlineStr">
         <is>
-          <t>5.5 / 10 SOLID</t>
+          <t>7.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O76" t="inlineStr">
@@ -6513,40 +6513,40 @@
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>CHAMBLFERT</t>
+          <t>BAJAJFINSV</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
+          <t>Bajaj Finserv Ltd.</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>418.3</v>
+        <v>1970</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>487.44 - 491.19 RD SUPPLY</t>
+          <t>1939.2 - 1951.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>404.75 - 434.2 DR DEMAND</t>
+          <t>1991.7 - 2073.13 RD SUPPLY</t>
         </is>
       </c>
       <c r="I77" t="inlineStr">
@@ -6556,12 +6556,12 @@
       </c>
       <c r="J77" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K77" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L77" t="inlineStr">
@@ -6571,12 +6571,12 @@
       </c>
       <c r="M77" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N77" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O77" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>ENRIN</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>HDFC Life Insurance Company Ltd.</t>
+          <t>Siemens Energy India Ltd.</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D78" t="inlineStr">
@@ -6612,26 +6612,26 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>533.5</v>
+        <v>3115.7</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>530.5 - 535.95 DR DEMAND</t>
+          <t>3075.0 - 3121.7 DR DEMAND</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>811.41 - 817.84 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I78" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J78" t="inlineStr">
@@ -6641,7 +6641,7 @@
       </c>
       <c r="K78" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L78" t="inlineStr">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="N78" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O78" t="inlineStr">
@@ -6673,17 +6673,17 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>HINDCOPPER</t>
+          <t>MSUMI</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Hindustan Copper Ltd.</t>
+          <t>Motherson Sumi Wiring India Ltd.</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>AUTO</t>
         </is>
       </c>
       <c r="D79" t="inlineStr">
@@ -6692,26 +6692,26 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>518.5</v>
+        <v>36.52</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>515.0 - 529.05 DR DEMAND</t>
+          <t>35.19 - 35.38 DR DEMAND</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>445.7 - 453.5 DR DEMAND</t>
+          <t>36.14 - 36.57 DR DEMAND</t>
         </is>
       </c>
       <c r="I79" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J79" t="inlineStr">
@@ -6721,7 +6721,7 @@
       </c>
       <c r="K79" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L79" t="inlineStr">
@@ -6736,7 +6736,7 @@
       </c>
       <c r="N79" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O79" t="inlineStr">
@@ -6753,17 +6753,17 @@
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>RITES</t>
+          <t>UTIAMC</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>RITES Ltd.</t>
+          <t>UTI Asset Management Company Ltd.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
@@ -6772,26 +6772,26 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>213.78</v>
+        <v>880.55</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>212.32 - 213.01 DR DEMAND</t>
+          <t>897.2 - 904.15 RD SUPPLY</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>217.6 - 229.47 RD SUPPLY</t>
+          <t>841.38 - 874.76 DR DEMAND</t>
         </is>
       </c>
       <c r="I80" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J80" t="inlineStr">
@@ -6801,7 +6801,7 @@
       </c>
       <c r="K80" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L80" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="N80" t="inlineStr">
         <is>
-          <t>5.0 / 10 SOLID</t>
+          <t>6.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O80" t="inlineStr">
@@ -6833,17 +6833,17 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>INTELLECT</t>
+          <t>HINDCOPPER</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Intellect Design Arena Ltd.</t>
+          <t>Hindustan Copper Ltd.</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D81" t="inlineStr">
@@ -6852,36 +6852,36 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>678.3</v>
+        <v>521.65</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>675.15 - 678.96 DR DEMAND</t>
+          <t>515.0 - 529.05 DR DEMAND</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>445.7 - 453.5 DR DEMAND</t>
         </is>
       </c>
       <c r="I81" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J81" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K81" t="inlineStr">
         <is>
-          <t>🔴 6 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L81" t="inlineStr">
@@ -6891,12 +6891,12 @@
       </c>
       <c r="M81" t="inlineStr">
         <is>
-          <t>+1.0 PT</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N81" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>6.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O81" t="inlineStr">
@@ -6913,45 +6913,45 @@
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>JSWCEMENT</t>
+          <t>BATAINDIA</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JSW Cement Ltd.</t>
+          <t>Bata India Ltd.</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>DEMAND</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>123.37</v>
+        <v>672.75</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>122.35 - 124.18 DR DEMAND</t>
+          <t>666.85 - 670.45 DR DEMAND</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>685.67 - 743.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="I82" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J82" t="inlineStr">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="K82" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L82" t="inlineStr">
@@ -6971,12 +6971,12 @@
       </c>
       <c r="M82" t="inlineStr">
         <is>
-          <t>+2.0 PTS</t>
+          <t>+0.0 PTS</t>
         </is>
       </c>
       <c r="N82" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O82" t="inlineStr">
@@ -6986,24 +6986,24 @@
       </c>
       <c r="P82" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>RHIM</t>
+          <t>CHAMBLFERT</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>RHI MAGNESITA INDIA LTD.</t>
+          <t>Chambal Fertilizers &amp; Chemicals Ltd.</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D83" t="inlineStr">
@@ -7012,26 +7012,26 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>369.75</v>
+        <v>419.05</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>366.95 - 370.0 DR DEMAND</t>
+          <t>487.44 - 491.19 RD SUPPLY</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>323.05 - 337.85 DR DEMAND</t>
+          <t>404.75 - 434.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I83" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="J83" t="inlineStr">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="K83" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L83" t="inlineStr">
@@ -7056,7 +7056,7 @@
       </c>
       <c r="N83" t="inlineStr">
         <is>
-          <t>4.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O83" t="inlineStr">
@@ -7073,12 +7073,12 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>MAXHEALTH</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Dr. Reddy's Laboratories Ltd.</t>
+          <t>Max Healthcare Institute Ltd.</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
@@ -7092,21 +7092,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1155</v>
+        <v>984.8</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>980.3 - 990.5 DR DEMAND</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>1141.16 - 1182.0 DR DEMAND</t>
+          <t>937.3 - 958.19 DR DEMAND</t>
         </is>
       </c>
       <c r="I84" t="inlineStr">
@@ -7121,7 +7121,7 @@
       </c>
       <c r="K84" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L84" t="inlineStr">
@@ -7136,7 +7136,7 @@
       </c>
       <c r="N84" t="inlineStr">
         <is>
-          <t>3.5 / 10 SOLID</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O84" t="inlineStr">
@@ -7153,45 +7153,45 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>CCL</t>
+          <t>RITES</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>CCL Products (I) Ltd.</t>
+          <t>RITES Ltd.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>EQUILIBRIUM</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1107.3</v>
+        <v>215.8</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>1119.98 - 1123.77 RD SUPPLY</t>
+          <t>212.32 - 213.01 DR DEMAND</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>1040.1 - 1050.87 DR DEMAND</t>
+          <t>217.6 - 229.47 RD SUPPLY</t>
         </is>
       </c>
       <c r="I85" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J85" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="K85" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L85" t="inlineStr">
@@ -7216,62 +7216,62 @@
       </c>
       <c r="N85" t="inlineStr">
         <is>
-          <t>9.0 / 10 SUPPLY</t>
+          <t>5.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O85" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>CONFLICT</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>JSWCEMENT</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Blue Star Ltd.</t>
+          <t>JSW Cement Ltd.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1485.7</v>
+        <v>124.07</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>1491.0 - 1499.0 RD SUPPLY</t>
+          <t>122.35 - 124.18 DR DEMAND</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>1772.31 - 1919.49 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I86" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J86" t="inlineStr">
@@ -7281,7 +7281,7 @@
       </c>
       <c r="K86" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 5 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L86" t="inlineStr">
@@ -7291,67 +7291,67 @@
       </c>
       <c r="M86" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+2.0 PTS</t>
         </is>
       </c>
       <c r="N86" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O86" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P86" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>BERGEPAINT</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Fortis Healthcare Ltd.</t>
+          <t>Berger Paints India Ltd.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>917.5</v>
+        <v>485.3</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>929.0 - 941.9 RD SUPPLY</t>
+          <t>485.24 - 486.03 DR DEMAND</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>765.99 - 794.16 DR DEMAND</t>
+          <t>560.77 - 590.09 RD SUPPLY</t>
         </is>
       </c>
       <c r="I87" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J87" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K87" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L87" t="inlineStr">
@@ -7371,67 +7371,67 @@
       </c>
       <c r="M87" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N87" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SOLID</t>
         </is>
       </c>
       <c r="O87" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>MUTHOOTFIN</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Muthoot Finance Ltd.</t>
+          <t>Dr. Reddy's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>2926.5</v>
+        <v>1151</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2975.0 - 2985.9 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>2064.17 - 2088.91 DR DEMAND</t>
+          <t>1141.16 - 1182.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
@@ -7441,7 +7441,7 @@
       </c>
       <c r="K88" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L88" t="inlineStr">
@@ -7451,67 +7451,67 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N88" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>VMM</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Power Grid Corporation of India Ltd.</t>
+          <t>Vishal Mega Mart Ltd.</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>SUPPLY</t>
+          <t>DEMAND</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>265.6</v>
+        <v>106.14</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>269.9 - 270.75 RD SUPPLY</t>
+          <t>105.8 - 107.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>239.47 - 242.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
@@ -7521,7 +7521,7 @@
       </c>
       <c r="K89" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L89" t="inlineStr">
@@ -7531,39 +7531,39 @@
       </c>
       <c r="M89" t="inlineStr">
         <is>
-          <t>+0.0 PTS</t>
+          <t>+1.0 PT</t>
         </is>
       </c>
       <c r="N89" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>3.5 / 10 SOLID</t>
         </is>
       </c>
       <c r="O89" t="inlineStr">
         <is>
-          <t>NEAR SUPPLY</t>
+          <t>WAIT FOR PULLBACK</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
         <is>
-          <t>NEAR</t>
+          <t>IN</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>PVRINOX</t>
+          <t>CCL</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>PVR INOX Ltd.</t>
+          <t>CCL Products (I) Ltd.</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D90" t="inlineStr">
@@ -7572,21 +7572,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>1247.5</v>
+        <v>1106.2</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>1255.3 - 1267.5 RD SUPPLY</t>
+          <t>1119.98 - 1123.77 RD SUPPLY</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>1207.7 - 1249.7 RD SUPPLY</t>
+          <t>1040.1 - 1050.87 DR DEMAND</t>
         </is>
       </c>
       <c r="I90" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="J90" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K90" t="inlineStr">
@@ -7616,7 +7616,7 @@
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>8.5 / 10 SUPPLY</t>
+          <t>9.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O90" t="inlineStr">
@@ -7633,17 +7633,17 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>UPL Ltd.</t>
+          <t>Blue Star Ltd.</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D91" t="inlineStr">
@@ -7652,11 +7652,11 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>585.35</v>
+        <v>1484</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>589.3 - 591.0 RD SUPPLY</t>
+          <t>1491.0 - 1499.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>557.75 - 565.72 DR DEMAND</t>
+          <t>1772.31 - 1919.49 RD SUPPLY</t>
         </is>
       </c>
       <c r="I91" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J91" t="inlineStr">
@@ -7713,17 +7713,17 @@
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Varun Beverages Ltd.</t>
+          <t>Power Grid Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D92" t="inlineStr">
@@ -7732,11 +7732,11 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>407.15</v>
+        <v>266</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>415.0 - 416.95 RD SUPPLY</t>
+          <t>269.9 - 270.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
@@ -7746,12 +7746,12 @@
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>520.87 - 531.92 RD SUPPLY</t>
+          <t>239.47 - 242.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I92" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J92" t="inlineStr">
@@ -7793,17 +7793,17 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ZENSARTECH</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Zensar Technolgies Ltd.</t>
+          <t>Varun Beverages Ltd.</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D93" t="inlineStr">
@@ -7812,11 +7812,11 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>465.45</v>
+        <v>407.6</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>472.95 - 475.55 RD SUPPLY</t>
+          <t>415.0 - 416.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -7826,12 +7826,12 @@
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>510.15 - 553.1 RD SUPPLY</t>
+          <t>520.87 - 531.92 RD SUPPLY</t>
         </is>
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J93" t="inlineStr">
@@ -7873,12 +7873,12 @@
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>KAJARIACER</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Indus Towers Ltd.</t>
+          <t>Kajaria Ceramics Ltd.</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -7892,31 +7892,31 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>374.95</v>
+        <v>1239.6</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>380.5 - 381.3 RD SUPPLY</t>
+          <t>1261.1 - 1269.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>427.61 - 433.1 RD SUPPLY</t>
+          <t>1187.65 - 1246.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="J94" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K94" t="inlineStr">
@@ -7953,12 +7953,12 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>MGL</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Reliance Industries Ltd.</t>
+          <t>Mahanagar Gas Ltd.</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -7972,11 +7972,11 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>1302.5</v>
+        <v>1096.6</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>1313.1 - 1321.9 RD SUPPLY</t>
+          <t>1115.3 - 1119.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
@@ -7986,12 +7986,12 @@
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>885.65 - 912.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I95" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J95" t="inlineStr">
@@ -8033,17 +8033,17 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>SRF Ltd.</t>
+          <t>APL Apollo Tubes Ltd.</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D96" t="inlineStr">
@@ -8052,31 +8052,31 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>2617</v>
+        <v>2250</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>2630.0 - 2644.7 RD SUPPLY</t>
+          <t>2265.6 - 2278.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>3066.4 - 3131.26 RD SUPPLY</t>
+          <t>2234.6 - 2301.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="I96" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J96" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K96" t="inlineStr">
@@ -8096,7 +8096,7 @@
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>8.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O96" t="inlineStr">
@@ -8132,7 +8132,7 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>787</v>
+        <v>785.75</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
@@ -8193,12 +8193,12 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>HDBFS</t>
+          <t>CRISIL</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>HDB Financial Services Ltd.</t>
+          <t>CRISIL Ltd.</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
@@ -8212,28 +8212,28 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>693.45</v>
+        <v>4802</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>700.0 - 701.0 RD SUPPLY</t>
+          <t>4325.1 - 4356.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
+          <t>7.0 A</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>4874.32 - 5005.77 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
           <t>7.5 A</t>
         </is>
       </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J98" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -8246,7 +8246,7 @@
       </c>
       <c r="L98" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M98" t="inlineStr">
@@ -8273,17 +8273,17 @@
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>SAREGAMA</t>
+          <t>LLOYDSME</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Saregama India Ltd</t>
+          <t>Lloyds Metals And Energy Ltd.</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D99" t="inlineStr">
@@ -8292,11 +8292,11 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>493.65</v>
+        <v>1823</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>493.75 - 496.95 RD SUPPLY</t>
+          <t>1848.7 - 1859.4 RD SUPPLY</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -8306,12 +8306,12 @@
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1042.28 - 1072.36 DR DEMAND</t>
         </is>
       </c>
       <c r="I99" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J99" t="inlineStr">
@@ -8353,17 +8353,17 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>SCI</t>
+          <t>NUVOCO</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Shipping Corporation of India Ltd.</t>
+          <t>Nuvoco Vistas Corporation Ltd.</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D100" t="inlineStr">
@@ -8372,26 +8372,26 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>294.95</v>
+        <v>352.15</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>299.05 - 303.7 RD SUPPLY</t>
+          <t>352.85 - 357.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>348.65 - 365.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="I100" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J100" t="inlineStr">
@@ -8401,12 +8401,12 @@
       </c>
       <c r="K100" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L100" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M100" t="inlineStr">
@@ -8433,12 +8433,12 @@
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>FSL</t>
+          <t>SAREGAMA</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Firstsource Solutions Ltd.</t>
+          <t>Saregama India Ltd</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
@@ -8452,16 +8452,16 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>265.3</v>
+        <v>492.75</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>270.4 - 272.0 RD SUPPLY</t>
+          <t>493.75 - 496.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -8496,7 +8496,7 @@
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>7.0 / 10 SUPPLY</t>
+          <t>7.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O101" t="inlineStr">
@@ -8513,17 +8513,17 @@
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>IRB</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Sun Pharmaceutical Industries Ltd.</t>
+          <t>IRB Infrastructure Developers Ltd.</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>PHARMA</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
@@ -8532,31 +8532,31 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1916</v>
+        <v>19.65</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>1932.0 - 1948.5 RD SUPPLY</t>
+          <t>19.85 - 20.04 RD SUPPLY</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>1569.37 - 1580.86 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J102" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K102" t="inlineStr">
@@ -8593,17 +8593,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>ZFCVINDIA</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ZF Commercial Vehicle Control Systems India Ltd.</t>
+          <t>Sun Pharmaceutical Industries Ltd.</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>AUTO</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D103" t="inlineStr">
@@ -8612,11 +8612,11 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>2524.8</v>
+        <v>1899</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>2572.2 - 2585.0 RD SUPPLY</t>
+          <t>1932.0 - 1948.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -8626,12 +8626,12 @@
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>2046.79 - 2067.08 DR DEMAND</t>
+          <t>1569.37 - 1580.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I103" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J103" t="inlineStr">
@@ -8673,17 +8673,17 @@
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>J&amp;KBANK</t>
+          <t>DIVISLAB</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Jammu &amp; Kashmir Bank Ltd.</t>
+          <t>Divi's Laboratories Ltd.</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D104" t="inlineStr">
@@ -8692,21 +8692,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>149.86</v>
+        <v>9100</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>151.37 - 152.17 RD SUPPLY</t>
+          <t>9244.0 - 9299.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>108.0 - 110.01 DR DEMAND</t>
+          <t>5624.31 - 5922.58 DR DEMAND</t>
         </is>
       </c>
       <c r="I104" t="inlineStr">
@@ -8716,12 +8716,12 @@
       </c>
       <c r="J104" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K104" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L104" t="inlineStr">
@@ -8753,17 +8753,17 @@
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>PNB</t>
+          <t>INTELLECT</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Punjab National Bank</t>
+          <t>Intellect Design Arena Ltd.</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="D105" t="inlineStr">
@@ -8772,36 +8772,36 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>116.32</v>
+        <v>686.65</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>117.95 - 118.25 RD SUPPLY</t>
+          <t>696.0 - 716.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>80.71 - 82.53 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I105" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J105" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K105" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L105" t="inlineStr">
@@ -8833,17 +8833,17 @@
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SARDAEN</t>
+          <t>J&amp;KBANK</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Sarda Energy and Minerals Ltd.</t>
+          <t>Jammu &amp; Kashmir Bank Ltd.</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>METAL</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D106" t="inlineStr">
@@ -8852,11 +8852,11 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>506.55</v>
+        <v>150.02</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>514.4 - 516.0 RD SUPPLY</t>
+          <t>151.37 - 152.17 RD SUPPLY</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -8866,12 +8866,12 @@
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>451.37 - 469.2 DR DEMAND</t>
+          <t>108.0 - 110.01 DR DEMAND</t>
         </is>
       </c>
       <c r="I106" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J106" t="inlineStr">
@@ -8881,7 +8881,7 @@
       </c>
       <c r="K106" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L106" t="inlineStr">
@@ -8913,12 +8913,12 @@
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SPLPETRO</t>
+          <t>NAVINFLUOR</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Supreme Petrochem Ltd.</t>
+          <t>Navin Fluorine International Ltd.</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
@@ -8932,11 +8932,11 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>725.8</v>
+        <v>8557.5</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>734.0 - 736.0 RD SUPPLY</t>
+          <t>8700.0 - 8718.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>457.27 - 563.79 DR DEMAND</t>
+          <t>4173.89 - 4245.43 DR DEMAND</t>
         </is>
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -8993,17 +8993,17 @@
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>SARDAEN</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Yes Bank Ltd.</t>
+          <t>Sarda Energy and Minerals Ltd.</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>BANK</t>
+          <t>METAL</t>
         </is>
       </c>
       <c r="D108" t="inlineStr">
@@ -9012,11 +9012,11 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>22.54</v>
+        <v>508.55</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>22.92 - 23.02 RD SUPPLY</t>
+          <t>514.4 - 516.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
@@ -9026,12 +9026,12 @@
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>451.37 - 469.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J108" t="inlineStr">
@@ -9041,7 +9041,7 @@
       </c>
       <c r="K108" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L108" t="inlineStr">
@@ -9073,17 +9073,17 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>CLEAN</t>
+          <t>EMCURE</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Clean Science and Technology Ltd.</t>
+          <t>Emcure Pharmaceuticals Ltd.</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>PHARMA</t>
         </is>
       </c>
       <c r="D109" t="inlineStr">
@@ -9092,28 +9092,28 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>852.95</v>
+        <v>1927.6</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>868.0 - 874.8 RD SUPPLY</t>
+          <t>1834.83 - 1851.1 DR DEMAND</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
+          <t>8.5 A</t>
+        </is>
+      </c>
+      <c r="H109" t="inlineStr">
+        <is>
+          <t>1962.18 - 2044.02 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H109" t="inlineStr">
-        <is>
-          <t>1545.87 - 1590.61 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>5.5 B</t>
-        </is>
-      </c>
       <c r="J109" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -9126,7 +9126,7 @@
       </c>
       <c r="L109" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M109" t="inlineStr">
@@ -9153,17 +9153,17 @@
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LTFOODS</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>LT Foods Ltd.</t>
+          <t>IDFC First Bank Ltd.</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D110" t="inlineStr">
@@ -9172,11 +9172,11 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>442.55</v>
+        <v>86.70999999999999</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>448.05 - 453.3 RD SUPPLY</t>
+          <t>87.81 - 88.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>285.58 - 341.86 DR DEMAND</t>
+          <t>57.91 - 58.68 DR DEMAND</t>
         </is>
       </c>
       <c r="I110" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J110" t="inlineStr">
@@ -9233,17 +9233,17 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>HONASA</t>
+          <t>NLCINDIA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Honasa Consumer Ltd.</t>
+          <t>NLC India Ltd.</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D111" t="inlineStr">
@@ -9252,11 +9252,11 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>477.05</v>
+        <v>273.05</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>483.8 - 488.71 RD SUPPLY</t>
+          <t>274.75 - 276.8 RD SUPPLY</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
@@ -9266,17 +9266,17 @@
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>217.6 - 220.69 DR DEMAND</t>
         </is>
       </c>
       <c r="I111" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8.5 A</t>
         </is>
       </c>
       <c r="J111" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K111" t="inlineStr">
@@ -9296,7 +9296,7 @@
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O111" t="inlineStr">
@@ -9313,17 +9313,17 @@
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>SAMMAANCAP</t>
+          <t>PWL</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Sammaan Capital Ltd.</t>
+          <t>Physicswallah Ltd.</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
@@ -9332,41 +9332,41 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>153.7</v>
+        <v>126.42</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>154.5 - 158.49 RD SUPPLY</t>
+          <t>127.6 - 129.88 RD SUPPLY</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>134.75 - 144.61 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I112" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J112" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K112" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L112" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M112" t="inlineStr">
@@ -9376,7 +9376,7 @@
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O112" t="inlineStr">
@@ -9393,17 +9393,17 @@
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>SUNDARMFIN</t>
+          <t>TATACOMM</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Sundaram Finance Ltd.</t>
+          <t>Tata Communications Ltd.</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D113" t="inlineStr">
@@ -9412,26 +9412,26 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4578</v>
+        <v>1756.1</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>4625.4 - 4658.0 RD SUPPLY</t>
+          <t>1758.2 - 1779.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>5480.6 - 5612.41 RD SUPPLY</t>
+          <t>1310.58 - 1335.75 DR DEMAND</t>
         </is>
       </c>
       <c r="I113" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J113" t="inlineStr">
@@ -9456,7 +9456,7 @@
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>5.0 / 10 SUPPLY</t>
+          <t>6.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O113" t="inlineStr">
@@ -9473,17 +9473,17 @@
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>KARURVYSYA</t>
+          <t>COHANCE</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Karur Vysya Bank Ltd.</t>
+          <t>Cohance Lifesciences Ltd.</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D114" t="inlineStr">
@@ -9492,26 +9492,26 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>350</v>
+        <v>456.6</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>356.85 - 358.65 RD SUPPLY</t>
+          <t>462.35 - 467.2 RD SUPPLY</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1229.95 - 1328.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I114" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J114" t="inlineStr">
@@ -9521,7 +9521,7 @@
       </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🟢 0 TESTS (FRESH)</t>
         </is>
       </c>
       <c r="L114" t="inlineStr">
@@ -9536,7 +9536,7 @@
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O114" t="inlineStr">
@@ -9553,17 +9553,17 @@
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>KPRMILL</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>K.P.R. Mill Ltd.</t>
+          <t>UPL Ltd.</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D115" t="inlineStr">
@@ -9572,11 +9572,11 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>1175.4</v>
+        <v>582.15</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>885.21 - 891.84 DR DEMAND</t>
+          <t>589.3 - 591.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
@@ -9586,7 +9586,7 @@
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>1179.41 - 1331.08 RD SUPPLY</t>
+          <t>557.75 - 565.72 DR DEMAND</t>
         </is>
       </c>
       <c r="I115" t="inlineStr">
@@ -9596,7 +9596,7 @@
       </c>
       <c r="J115" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K115" t="inlineStr">
@@ -9616,7 +9616,7 @@
       </c>
       <c r="N115" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O115" t="inlineStr">
@@ -9633,17 +9633,17 @@
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>GRAPHITE</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>LIC Housing Finance Ltd.</t>
+          <t>Graphite India Ltd.</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D116" t="inlineStr">
@@ -9652,26 +9652,26 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>554</v>
+        <v>733.6</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>485.45 - 490.0 DR DEMAND</t>
+          <t>739.9 - 744.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>554.86 - 559.52 RD SUPPLY</t>
+          <t>551.99 - 610.0 DR DEMAND</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J116" t="inlineStr">
@@ -9686,7 +9686,7 @@
       </c>
       <c r="L116" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M116" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="N116" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O116" t="inlineStr">
@@ -9713,17 +9713,17 @@
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>OBEROIRLTY</t>
+          <t>LTFOODS</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Oberoi Realty Ltd.</t>
+          <t>LT Foods Ltd.</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>REALTY</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D117" t="inlineStr">
@@ -9732,26 +9732,26 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1902</v>
+        <v>444.8</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>1950.4 - 1960.7 RD SUPPLY</t>
+          <t>451.3 - 456.55 RD SUPPLY</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>1903.46 - 1993.03 RD SUPPLY</t>
+          <t>285.58 - 341.86 DR DEMAND</t>
         </is>
       </c>
       <c r="I117" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="J117" t="inlineStr">
@@ -9766,7 +9766,7 @@
       </c>
       <c r="L117" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M117" t="inlineStr">
@@ -9776,7 +9776,7 @@
       </c>
       <c r="N117" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O117" t="inlineStr">
@@ -9793,17 +9793,17 @@
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>USHAMART</t>
+          <t>BALRAMCHIN</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Usha Martin Ltd.</t>
+          <t>Balrampur Chini Mills Ltd.</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>FMCG</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
@@ -9812,11 +9812,11 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>515.65</v>
+        <v>690.6</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>520.99 - 523.57 RD SUPPLY</t>
+          <t>695.95 - 738.95 RD SUPPLY</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>274.28 - 291.22 DR DEMAND</t>
+          <t>415.9 - 440.91 DR DEMAND</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -9873,17 +9873,17 @@
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>CENTRALBK</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Adani Ports and Special Economic Zone Ltd.</t>
+          <t>Central Bank of India</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D119" t="inlineStr">
@@ -9892,36 +9892,36 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1706.5</v>
+        <v>31.08</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>1711.9 - 1719.7 RD SUPPLY</t>
+          <t>31.46 - 31.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>1288.07 - 1307.09 DR DEMAND</t>
+          <t>35.83 - 36.93 RD SUPPLY</t>
         </is>
       </c>
       <c r="I119" t="inlineStr">
         <is>
-          <t>9.0 A+</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J119" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K119" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L119" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="N119" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O119" t="inlineStr">
@@ -9953,17 +9953,17 @@
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>COHANCE</t>
+          <t>OBEROIRLTY</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Cohance Lifesciences Ltd.</t>
+          <t>Oberoi Realty Ltd.</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>REALTY</t>
         </is>
       </c>
       <c r="D120" t="inlineStr">
@@ -9972,26 +9972,26 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>460.85</v>
+        <v>1875.6</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>462.35 - 467.2 RD SUPPLY</t>
+          <t>1950.4 - 1960.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>1229.95 - 1328.0 RD SUPPLY</t>
+          <t>1903.46 - 1993.03 RD SUPPLY</t>
         </is>
       </c>
       <c r="I120" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J120" t="inlineStr">
@@ -10016,7 +10016,7 @@
       </c>
       <c r="N120" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O120" t="inlineStr">
@@ -10033,17 +10033,17 @@
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>RAINBOW</t>
+          <t>PNB</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Rainbow Childrens Medicare Ltd.</t>
+          <t>Punjab National Bank</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>HEALTHCARE</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D121" t="inlineStr">
@@ -10052,21 +10052,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1440.8</v>
+        <v>117</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>1465.0 - 1471.0 RD SUPPLY</t>
+          <t>117.95 - 118.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>1550.0 - 1610.0 RD SUPPLY</t>
+          <t>80.71 - 82.53 DR DEMAND</t>
         </is>
       </c>
       <c r="I121" t="inlineStr">
@@ -10081,7 +10081,7 @@
       </c>
       <c r="K121" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L121" t="inlineStr">
@@ -10096,7 +10096,7 @@
       </c>
       <c r="N121" t="inlineStr">
         <is>
-          <t>4.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O121" t="inlineStr">
@@ -10113,17 +10113,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>KIRLOSENG</t>
+          <t>SCI</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Kirloskar Oil Eng Ltd.</t>
+          <t>Shipping Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D122" t="inlineStr">
@@ -10132,26 +10132,26 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>2267.6</v>
+        <v>295.35</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2278.28 - 2293.15 RD SUPPLY</t>
+          <t>298.04 - 302.67 RD SUPPLY</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>3.5 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>539.93 - 571.37 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J122" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="K122" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L122" t="inlineStr">
         <is>
-          <t>🔥 2.5x VOL EXPLOSION</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M122" t="inlineStr">
@@ -10176,7 +10176,7 @@
       </c>
       <c r="N122" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O122" t="inlineStr">
@@ -10193,17 +10193,17 @@
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ABB India Ltd.</t>
+          <t>Union Bank of India</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>PSUBANK</t>
         </is>
       </c>
       <c r="D123" t="inlineStr">
@@ -10212,26 +10212,26 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>7432</v>
+        <v>187.22</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>7578.29 - 7832.29 RD SUPPLY</t>
+          <t>187.93 - 189.46 RD SUPPLY</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>196.47 - 199.6 RD SUPPLY</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.5 A</t>
         </is>
       </c>
       <c r="J123" t="inlineStr">
@@ -10241,7 +10241,7 @@
       </c>
       <c r="K123" t="inlineStr">
         <is>
-          <t>🔴 4 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L123" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="N123" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O123" t="inlineStr">
@@ -10273,17 +10273,17 @@
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>CHALET</t>
+          <t>USHAMART</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Chalet Hotels Ltd.</t>
+          <t>Usha Martin Ltd.</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
@@ -10292,26 +10292,26 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>890.75</v>
+        <v>514.15</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>899.9 - 914.0 RD SUPPLY</t>
+          <t>520.99 - 523.57 RD SUPPLY</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>973.92 - 1051.29 RD SUPPLY</t>
+          <t>274.28 - 291.22 DR DEMAND</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J124" t="inlineStr">
@@ -10321,12 +10321,12 @@
       </c>
       <c r="K124" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L124" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M124" t="inlineStr">
@@ -10336,7 +10336,7 @@
       </c>
       <c r="N124" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O124" t="inlineStr">
@@ -10353,17 +10353,17 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>KOTAKBANK</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>City Union Bank Ltd.</t>
+          <t>Kotak Mahindra Bank Ltd.</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>PVTBANK</t>
+          <t>BANK</t>
         </is>
       </c>
       <c r="D125" t="inlineStr">
@@ -10372,26 +10372,26 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>234.36</v>
+        <v>424.5</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>235.93 - 243.1 RD SUPPLY</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>177.59 - 189.81 DR DEMAND</t>
+          <t>431.46 - 447.25 RD SUPPLY</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
         <is>
-          <t>7.0 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J125" t="inlineStr">
@@ -10401,7 +10401,7 @@
       </c>
       <c r="K125" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L125" t="inlineStr">
@@ -10416,7 +10416,7 @@
       </c>
       <c r="N125" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O125" t="inlineStr">
@@ -10433,17 +10433,17 @@
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>FINCABLES</t>
+          <t>RAINBOW</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>Finolex Cables Ltd.</t>
+          <t>Rainbow Childrens Medicare Ltd.</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>HEALTHCARE</t>
         </is>
       </c>
       <c r="D126" t="inlineStr">
@@ -10452,26 +10452,26 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>1272.9</v>
+        <v>1447.2</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>1291.9 - 1307.5 RD SUPPLY</t>
+          <t>1465.0 - 1471.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>956.2 - 987.6 DR DEMAND</t>
+          <t>1550.0 - 1610.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="I126" t="inlineStr">
         <is>
-          <t>8.0 A</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J126" t="inlineStr">
@@ -10496,7 +10496,7 @@
       </c>
       <c r="N126" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O126" t="inlineStr">
@@ -10513,17 +10513,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>JSWDULUX</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>JSW Dulux Ltd.</t>
+          <t>Reliance Industries Ltd.</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>CONSUMPTION</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D127" t="inlineStr">
@@ -10532,11 +10532,11 @@
         </is>
       </c>
       <c r="E127" t="n">
-        <v>3167.6</v>
+        <v>1322</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>3169.9 - 3195.0 RD SUPPLY</t>
+          <t>1328.9 - 1344.9 RD SUPPLY</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
@@ -10546,22 +10546,22 @@
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>2862.0 - 2938.8 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I127" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J127" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K127" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L127" t="inlineStr">
@@ -10576,7 +10576,7 @@
       </c>
       <c r="N127" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O127" t="inlineStr">
@@ -10593,17 +10593,17 @@
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>TEJASNET</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Bharat Petroleum Corporation Ltd.</t>
+          <t>Tejas Networks Ltd.</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D128" t="inlineStr">
@@ -10612,26 +10612,26 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>320.05</v>
+        <v>614.15</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>326.35 - 330.35 RD SUPPLY</t>
+          <t>491.95 - 494.3 DR DEMAND</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>2.5 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>219.64 - 222.73 DR DEMAND</t>
+          <t>615.0 - 644.75 RD SUPPLY</t>
         </is>
       </c>
       <c r="I128" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J128" t="inlineStr">
@@ -10641,12 +10641,12 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L128" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M128" t="inlineStr">
@@ -10656,7 +10656,7 @@
       </c>
       <c r="N128" t="inlineStr">
         <is>
-          <t>2.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">
@@ -10673,17 +10673,17 @@
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>NIACL</t>
+          <t>HEG</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>The New India Assurance Company Ltd.</t>
+          <t>H.E.G. Ltd.</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>INFRA</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
@@ -10692,26 +10692,26 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>195.33</v>
+        <v>728.25</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>192.07 - 199.99 RD SUPPLY</t>
+          <t>741.0 - 749.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>488.19 - 524.73 DR DEMAND</t>
         </is>
       </c>
       <c r="I129" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J129" t="inlineStr">
@@ -10721,12 +10721,12 @@
       </c>
       <c r="K129" t="inlineStr">
         <is>
-          <t>🟢 0 TESTS (FRESH)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L129" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M129" t="inlineStr">
@@ -10736,34 +10736,34 @@
       </c>
       <c r="N129" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O129" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P129" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>NLCINDIA</t>
+          <t>CHALET</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>NLC India Ltd.</t>
+          <t>Chalet Hotels Ltd.</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D130" t="inlineStr">
@@ -10772,36 +10772,36 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>274.9</v>
+        <v>896.75</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>274.75 - 276.8 RD SUPPLY</t>
+          <t>899.9 - 914.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>3.0 C</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>217.6 - 220.69 DR DEMAND</t>
+          <t>973.92 - 1051.29 RD SUPPLY</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>8.5 A</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="J130" t="inlineStr">
         <is>
-          <t>1W DOWN • 20 EMA BEARISH</t>
+          <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
       <c r="K130" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 3 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L130" t="inlineStr">
@@ -10816,29 +10816,29 @@
       </c>
       <c r="N130" t="inlineStr">
         <is>
-          <t>6.0 / 10 SUPPLY</t>
+          <t>3.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P130" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>JUBLFOOD</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Jubilant Foodworks Ltd.</t>
+          <t>Adani Ports and Special Economic Zone Ltd.</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
@@ -10852,26 +10852,26 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>482.9</v>
+        <v>1707.3</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>408.55 - 410.0 DR DEMAND</t>
+          <t>1711.9 - 1719.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>6.0 B</t>
+          <t>2.5 C</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>477.24 - 497.34 RD SUPPLY</t>
+          <t>1288.07 - 1307.09 DR DEMAND</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>5.5 B</t>
+          <t>9.0 A+</t>
         </is>
       </c>
       <c r="J131" t="inlineStr">
@@ -10881,7 +10881,7 @@
       </c>
       <c r="K131" t="inlineStr">
         <is>
-          <t>🟡 1 TEST (TESTED)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L131" t="inlineStr">
@@ -10896,29 +10896,29 @@
       </c>
       <c r="N131" t="inlineStr">
         <is>
-          <t>5.5 / 10 SUPPLY</t>
+          <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O131" t="inlineStr">
         <is>
-          <t>SUPPLY TEST</t>
+          <t>NEAR SUPPLY</t>
         </is>
       </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>IN</t>
+          <t>NEAR</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>REDINGTON</t>
+          <t>JUBLFOOD</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Redington Ltd.</t>
+          <t>Jubilant Foodworks Ltd.</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
@@ -10932,28 +10932,28 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>372.45</v>
+        <v>482.7</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>366.5 - 378.5 RD SUPPLY</t>
+          <t>408.55 - 410.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr">
+        <is>
+          <t>477.24 - 497.34 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
           <t>5.5 B</t>
         </is>
       </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>— NO ACTIVE ZONE —</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="J132" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -10966,7 +10966,7 @@
       </c>
       <c r="L132" t="inlineStr">
         <is>
-          <t>🔥 1.8x HIGH VOL</t>
+          <t>NORMAL VOL</t>
         </is>
       </c>
       <c r="M132" t="inlineStr">
@@ -10993,17 +10993,17 @@
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>BALRAMCHIN</t>
+          <t>REDINGTON</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Balrampur Chini Mills Ltd.</t>
+          <t>Redington Ltd.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>FMCG</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D133" t="inlineStr">
@@ -11012,26 +11012,26 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>704.35</v>
+        <v>371.3</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>695.95 - 738.95 RD SUPPLY</t>
+          <t>366.5 - 378.5 RD SUPPLY</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>5.5 B</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>415.9 - 440.91 DR DEMAND</t>
+          <t>— NO ACTIVE ZONE —</t>
         </is>
       </c>
       <c r="I133" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>—</t>
         </is>
       </c>
       <c r="J133" t="inlineStr">
@@ -11056,7 +11056,7 @@
       </c>
       <c r="N133" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O133" t="inlineStr">
@@ -11073,12 +11073,12 @@
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>SAMMAANCAP</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>SBI Cards and Payment Services Ltd.</t>
+          <t>Sammaan Capital Ltd.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
@@ -11092,21 +11092,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>661</v>
+        <v>158.39</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>653.2 - 668.45 RD SUPPLY</t>
+          <t>154.5 - 158.49 RD SUPPLY</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>4.5 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>565.45 - 593.2 DR DEMAND</t>
+          <t>143.86 - 146.31 DR DEMAND</t>
         </is>
       </c>
       <c r="I134" t="inlineStr">
@@ -11116,7 +11116,7 @@
       </c>
       <c r="J134" t="inlineStr">
         <is>
-          <t>1W UP • 20 EMA BULLISH</t>
+          <t>1W DOWN • 20 EMA BEARISH</t>
         </is>
       </c>
       <c r="K134" t="inlineStr">
@@ -11136,7 +11136,7 @@
       </c>
       <c r="N134" t="inlineStr">
         <is>
-          <t>4.5 / 10 SUPPLY</t>
+          <t>5.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O134" t="inlineStr">
@@ -11153,17 +11153,17 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>TITAGARH</t>
+          <t>KPRMILL</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Titagarh Rail Systems Ltd.</t>
+          <t>K.P.R. Mill Ltd.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>INFRA</t>
+          <t>CONSUMPTION</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
@@ -11172,11 +11172,11 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>844.2</v>
+        <v>1186.3</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>839.45 - 852.15 RD SUPPLY</t>
+          <t>885.21 - 891.84 DR DEMAND</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -11186,12 +11186,12 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>1179.41 - 1331.08 RD SUPPLY</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4.5 C</t>
         </is>
       </c>
       <c r="J135" t="inlineStr">
@@ -11233,17 +11233,17 @@
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Union Bank of India</t>
+          <t>SBI Cards and Payment Services Ltd.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>PSUBANK</t>
+          <t>FINSERVICE</t>
         </is>
       </c>
       <c r="D136" t="inlineStr">
@@ -11252,11 +11252,11 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>189</v>
+        <v>658.25</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>187.93 - 189.46 RD SUPPLY</t>
+          <t>653.2 - 668.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
@@ -11266,12 +11266,12 @@
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>196.47 - 199.6 RD SUPPLY</t>
+          <t>565.45 - 593.2 DR DEMAND</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>6.5 B</t>
         </is>
       </c>
       <c r="J136" t="inlineStr">
@@ -11313,17 +11313,17 @@
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>HOMEFIRST</t>
+          <t>CASTROLIND</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Home First Finance Company India Ltd.</t>
+          <t>Castrol India Ltd.</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D137" t="inlineStr">
@@ -11332,26 +11332,26 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>1201.4</v>
+        <v>190.27</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>1151.9 - 1160.0 DR DEMAND</t>
+          <t>189.0 - 190.45 RD SUPPLY</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>5.0 C</t>
+          <t>4.0 C</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>1184.37 - 1233.14 RD SUPPLY</t>
+          <t>144.37 - 156.26 DR DEMAND</t>
         </is>
       </c>
       <c r="I137" t="inlineStr">
         <is>
-          <t>4.0 C</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="J137" t="inlineStr">
@@ -11366,7 +11366,7 @@
       </c>
       <c r="L137" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 1.8x HIGH VOL</t>
         </is>
       </c>
       <c r="M137" t="inlineStr">
@@ -11393,12 +11393,12 @@
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>LICI</t>
+          <t>HOMEFIRST</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Life Insurance Corporation of India</t>
+          <t>Home First Finance Company India Ltd.</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
@@ -11412,21 +11412,21 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>416.9</v>
+        <v>1210.1</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>406.8 - 408.25 DR DEMAND</t>
+          <t>1151.9 - 1160.0 DR DEMAND</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>5.0 C</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>414.97 - 443.6 RD SUPPLY</t>
+          <t>1184.37 - 1233.14 RD SUPPLY</t>
         </is>
       </c>
       <c r="I138" t="inlineStr">
@@ -11441,7 +11441,7 @@
       </c>
       <c r="K138" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🟡 1 TEST (TESTED)</t>
         </is>
       </c>
       <c r="L138" t="inlineStr">
@@ -11473,17 +11473,17 @@
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>CONCOR</t>
+          <t>IGL</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Container Corporation of India Ltd.</t>
+          <t>Indraprastha Gas Ltd.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CPSE</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="D139" t="inlineStr">
@@ -11492,28 +11492,28 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>508.85</v>
+        <v>158.04</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>447.08 - 450.02 DR DEMAND</t>
+          <t>155.0 - 158.7 RD SUPPLY</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
+          <t>4.0 C</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>141.74 - 145.62 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H139" t="inlineStr">
-        <is>
-          <t>507.3 - 535.36 RD SUPPLY</t>
-        </is>
-      </c>
-      <c r="I139" t="inlineStr">
-        <is>
-          <t>3.5 C</t>
-        </is>
-      </c>
       <c r="J139" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
@@ -11521,12 +11521,12 @@
       </c>
       <c r="K139" t="inlineStr">
         <is>
-          <t>🔴 2 TESTS (WEAK)</t>
+          <t>🔴 4 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L139" t="inlineStr">
         <is>
-          <t>NORMAL VOL</t>
+          <t>🔥 2.5x VOL EXPLOSION</t>
         </is>
       </c>
       <c r="M139" t="inlineStr">
@@ -11536,7 +11536,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>3.5 / 10 SUPPLY</t>
+          <t>4.0 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O139" t="inlineStr">
@@ -11553,17 +11553,17 @@
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>BAJAJFINSV</t>
+          <t>CONCOR</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Bajaj Finserv Ltd.</t>
+          <t>Container Corporation of India Ltd.</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>CPSE</t>
         </is>
       </c>
       <c r="D140" t="inlineStr">
@@ -11572,26 +11572,26 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1992.1</v>
+        <v>508</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>1939.2 - 1951.5 DR DEMAND</t>
+          <t>447.08 - 450.02 DR DEMAND</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>6.5 B</t>
+          <t>6.0 B</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>1991.7 - 2073.13 RD SUPPLY</t>
+          <t>507.3 - 535.36 RD SUPPLY</t>
         </is>
       </c>
       <c r="I140" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="J140" t="inlineStr">
@@ -11616,7 +11616,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O140" t="inlineStr">
@@ -11633,12 +11633,12 @@
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>POONAWALLA</t>
+          <t>SUNDARMFIN</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>Poonawalla Fincorp Ltd.</t>
+          <t>Sundaram Finance Ltd.</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
@@ -11652,26 +11652,26 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>465.1</v>
+        <v>4648.7</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>425.0 - 428.45 DR DEMAND</t>
+          <t>4625.4 - 4658.0 RD SUPPLY</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>7.5 A</t>
+          <t>3.5 C</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>454.8 - 503.0 RD SUPPLY</t>
+          <t>5480.6 - 5612.41 RD SUPPLY</t>
         </is>
       </c>
       <c r="I141" t="inlineStr">
         <is>
-          <t>3.0 C</t>
+          <t>8.0 A</t>
         </is>
       </c>
       <c r="J141" t="inlineStr">
@@ -11681,7 +11681,7 @@
       </c>
       <c r="K141" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L141" t="inlineStr">
@@ -11696,7 +11696,7 @@
       </c>
       <c r="N141" t="inlineStr">
         <is>
-          <t>3.0 / 10 SUPPLY</t>
+          <t>3.5 / 10 SUPPLY</t>
         </is>
       </c>
       <c r="O141" t="inlineStr">
@@ -11713,17 +11713,17 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>SBFC</t>
+          <t>CUB</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
         <is>
-          <t>SBFC Finance Ltd.</t>
+          <t>City Union Bank Ltd.</t>
         </is>
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>FINSERVICE</t>
+          <t>PVTBANK</t>
         </is>
       </c>
       <c r="D142" t="inlineStr">
@@ -11732,11 +11732,11 @@
         </is>
       </c>
       <c r="E142" t="n">
-        <v>99.90000000000001</v>
+        <v>236.01</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>98.75 - 103.22 RD SUPPLY</t>
+          <t>235.93 - 243.1 RD SUPPLY</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
@@ -11746,12 +11746,12 @@
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>— NO ACTIVE ZONE —</t>
+          <t>177.59 - 189.81 DR DEMAND</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>7.0 A</t>
         </is>
       </c>
       <c r="J142" t="inlineStr">
@@ -11761,7 +11761,7 @@
       </c>
       <c r="K142" t="inlineStr">
         <is>
-          <t>🔴 3 TESTS (WEAK)</t>
+          <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
       <c r="L142" t="inlineStr">
@@ -11793,78 +11793,478 @@
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
+          <t>JSWDULUX</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>JSW Dulux Ltd.</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>CONSUMPTION</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>3174.5</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>3169.9 - 3195.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>2862.0 - 2938.8 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K143" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L143" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O143" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>POONAWALLA</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>Poonawalla Fincorp Ltd.</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>468.45</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>425.0 - 428.45 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>7.5 A</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>454.8 - 503.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L144" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M144" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O144" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>SBFC</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>SBFC Finance Ltd.</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>FINSERVICE</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E145" t="n">
+        <v>100.08</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>98.75 - 103.22 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G145" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H145" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I145" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J145" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K145" t="inlineStr">
+        <is>
+          <t>🔴 4 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L145" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M145" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N145" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O145" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P145" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>TITAGARH</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>Titagarh Rail Systems Ltd.</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>INFRA</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E146" t="n">
+        <v>871.85</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>867.2 - 873.0 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="G146" t="inlineStr">
+        <is>
+          <t>3.0 C</t>
+        </is>
+      </c>
+      <c r="H146" t="inlineStr">
+        <is>
+          <t>— NO ACTIVE ZONE —</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K146" t="inlineStr">
+        <is>
+          <t>🔴 3 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L146" t="inlineStr">
+        <is>
+          <t>🔥 2.5x VOL EXPLOSION</t>
+        </is>
+      </c>
+      <c r="M146" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N146" t="inlineStr">
+        <is>
+          <t>3.0 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O146" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P146" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>PCBL</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>PCBL Chemical Ltd.</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>FMCG</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>SUPPLY</t>
+        </is>
+      </c>
+      <c r="E147" t="n">
+        <v>317</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>308.15 - 309.8 DR DEMAND</t>
+        </is>
+      </c>
+      <c r="G147" t="inlineStr">
+        <is>
+          <t>6.0 B</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>305.14 - 326.1 RD SUPPLY</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>2.5 C</t>
+        </is>
+      </c>
+      <c r="J147" t="inlineStr">
+        <is>
+          <t>1W UP • 20 EMA BULLISH</t>
+        </is>
+      </c>
+      <c r="K147" t="inlineStr">
+        <is>
+          <t>🔴 2 TESTS (WEAK)</t>
+        </is>
+      </c>
+      <c r="L147" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>+0.0 PTS</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>2.5 / 10 SUPPLY</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>SUPPLY TEST</t>
+        </is>
+      </c>
+      <c r="P147" t="inlineStr">
+        <is>
+          <t>IN</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
           <t>PHOENIXLTD</t>
         </is>
       </c>
-      <c r="B143" t="inlineStr">
+      <c r="B148" t="inlineStr">
         <is>
           <t>Phoenix Mills Ltd.</t>
         </is>
       </c>
-      <c r="C143" t="inlineStr">
+      <c r="C148" t="inlineStr">
         <is>
           <t>REALTY</t>
         </is>
       </c>
-      <c r="D143" t="inlineStr">
+      <c r="D148" t="inlineStr">
         <is>
           <t>SUPPLY</t>
         </is>
       </c>
-      <c r="E143" t="n">
-        <v>1960</v>
-      </c>
-      <c r="F143" t="inlineStr">
+      <c r="E148" t="n">
+        <v>1942</v>
+      </c>
+      <c r="F148" t="inlineStr">
         <is>
           <t>2093.2 - 2099.9 RD SUPPLY</t>
         </is>
       </c>
-      <c r="G143" t="inlineStr">
+      <c r="G148" t="inlineStr">
         <is>
           <t>6.0 B</t>
         </is>
       </c>
-      <c r="H143" t="inlineStr">
+      <c r="H148" t="inlineStr">
         <is>
           <t>1853.5 - 1993.0 RD SUPPLY</t>
         </is>
       </c>
-      <c r="I143" t="inlineStr">
+      <c r="I148" t="inlineStr">
         <is>
           <t>2.5 C</t>
         </is>
       </c>
-      <c r="J143" t="inlineStr">
+      <c r="J148" t="inlineStr">
         <is>
           <t>1W UP • 20 EMA BULLISH</t>
         </is>
       </c>
-      <c r="K143" t="inlineStr">
+      <c r="K148" t="inlineStr">
         <is>
           <t>🔴 2 TESTS (WEAK)</t>
         </is>
       </c>
-      <c r="L143" t="inlineStr">
-        <is>
-          <t>NORMAL VOL</t>
-        </is>
-      </c>
-      <c r="M143" t="inlineStr">
+      <c r="L148" t="inlineStr">
+        <is>
+          <t>NORMAL VOL</t>
+        </is>
+      </c>
+      <c r="M148" t="inlineStr">
         <is>
           <t>+0.0 PTS</t>
         </is>
       </c>
-      <c r="N143" t="inlineStr">
+      <c r="N148" t="inlineStr">
         <is>
           <t>2.5 / 10 SUPPLY</t>
         </is>
       </c>
-      <c r="O143" t="inlineStr">
+      <c r="O148" t="inlineStr">
         <is>
           <t>SUPPLY TEST</t>
         </is>
       </c>
-      <c r="P143" t="inlineStr">
+      <c r="P148" t="inlineStr">
         <is>
           <t>IN</t>
         </is>
